--- a/tests/AddOn_Input_92111_v03.xlsx
+++ b/tests/AddOn_Input_92111_v03.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="29530"/>
-  <workbookPr defaultThemeVersion="202300"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="24334"/>
+  <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Horstmann\Documents\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\marco\Documents\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="8_{C01CCB04-CAA3-4236-8414-DCCC3CA4894C}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{7E0025BC-9204-4D1F-A25A-53A7D90806D3}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-57708" yWindow="-1308" windowWidth="29016" windowHeight="15696" xr2:uid="{FA0E1F60-FDE8-4B1B-B207-153282F6AB0E}"/>
+    <workbookView xWindow="-93" yWindow="-93" windowWidth="25786" windowHeight="13866" activeTab="3" xr2:uid="{FA0E1F60-FDE8-4B1B-B207-153282F6AB0E}"/>
   </bookViews>
   <sheets>
     <sheet name="Basics" sheetId="1" r:id="rId1"/>
@@ -32,16 +32,17 @@
         <xcalcf:feature name="microsoft.com:FV"/>
         <xcalcf:feature name="microsoft.com:CNMTM"/>
         <xcalcf:feature name="microsoft.com:LET_WF"/>
-        <xcalcf:feature name="microsoft.com:LAMBDA_WF"/>
-        <xcalcf:feature name="microsoft.com:ARRAYTEXT_WF"/>
       </xcalcf:calcFeatures>
+    </ext>
+    <ext xmlns:xlwcv="http://schemas.microsoft.com/office/spreadsheetml/2024/workbookCompatibilityVersion" uri="{D14903EA-33C4-47F7-8F05-3474C54BE107}">
+      <xlwcv:version setVersion="1"/>
     </ext>
   </extLst>
 </workbook>
 </file>
 
 <file path=xl/metadata.xml><?xml version="1.0" encoding="utf-8"?>
-<metadata xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:xlrd="http://schemas.microsoft.com/office/spreadsheetml/2017/richdata" xmlns:xda="http://schemas.microsoft.com/office/spreadsheetml/2017/dynamicarray">
+<metadata xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:xda="http://schemas.microsoft.com/office/spreadsheetml/2017/dynamicarray">
   <metadataTypes count="1">
     <metadataType name="XLDAPR" minSupportedVersion="120000" copy="1" pasteAll="1" pasteValues="1" merge="1" splitFirst="1" rowColShift="1" clearFormats="1" clearComments="1" assign="1" coerce="1" cellMeta="1"/>
   </metadataTypes>
@@ -63,7 +64,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="311" uniqueCount="169">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="314" uniqueCount="171">
   <si>
     <t>Kit Series:</t>
   </si>
@@ -232,9 +233,6 @@
     </r>
   </si>
   <si>
-    <t>Neuroleptics 2/EXTENDED 2 in serum/plasma</t>
-  </si>
-  <si>
     <t>92026/0/XT2</t>
   </si>
   <si>
@@ -247,9 +245,6 @@
     <t>92026/3/XT2</t>
   </si>
   <si>
-    <t>Plasma Calibrator Blank</t>
-  </si>
-  <si>
     <t>Plasma Calibrator Level 1</t>
   </si>
   <si>
@@ -581,13 +576,33 @@
   </si>
   <si>
     <t>Included Assays:</t>
+  </si>
+  <si>
+    <t>Reagent,Calibrator,Control,Deep Well Plate 96 well,Filter Plate 96 well,Collection Plate 96 well,Collection Plate 96 deep well,SPE Plate 96 well,Dilution Plate 96 Deep Well,Diilution Plate  96 well,Sample,Internal Standard</t>
+  </si>
+  <si>
+    <t>Pipette (1000), Pipette (300), Shake, Centrifuge, Collect, Dilute, Incubate</t>
+  </si>
+  <si>
+    <t>BG 7mL,
+BG 10mL,
+BG 30mL,
+BG 50mL,
+BG 100mL,
+Reaction Vials (33006),
+Sample Tube,
+Kabe Tube,
+Glass Tube 12mm</t>
+  </si>
+  <si>
+    <t>Plasma Calibrator Level 0</t>
   </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
-  <fonts count="8" x14ac:knownFonts="1">
+  <fonts count="8">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -695,7 +710,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="32">
+  <cellXfs count="33">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1"/>
@@ -717,8 +732,6 @@
     <xf numFmtId="0" fontId="1" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="1"/>
-    <xf numFmtId="0" fontId="4" fillId="3" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1"/>
-    <xf numFmtId="0" fontId="0" fillId="3" borderId="0" xfId="0" applyFill="1" applyAlignment="1"/>
     <xf numFmtId="0" fontId="1" fillId="3" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="0" fillId="3" borderId="1" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left"/>
@@ -729,9 +742,6 @@
     <xf numFmtId="0" fontId="4" fillId="3" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1"/>
     <xf numFmtId="0" fontId="0" fillId="3" borderId="0" xfId="0" applyFill="1" applyAlignment="1"/>
     <xf numFmtId="0" fontId="1" fillId="3" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
-    <xf numFmtId="0" fontId="1" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
@@ -753,6 +763,14 @@
     <xf numFmtId="0" fontId="7" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="1" fillId="3" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="left"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
+      <alignment wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="3" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1"/>
+    <xf numFmtId="0" fontId="0" fillId="3" borderId="0" xfId="0" applyFill="1" applyAlignment="1"/>
+    <xf numFmtId="0" fontId="1" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
     </xf>
   </cellXfs>
   <cellStyles count="1">
@@ -1104,7 +1122,7 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{4F699D14-CCD3-41DE-8802-28DD41EE9AAE}">
   <dimension ref="A1:H90"/>
-  <sheetFormatPr baseColWidth="10" defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
+  <sheetFormatPr baseColWidth="10" defaultRowHeight="13.7"/>
   <cols>
     <col min="1" max="1" width="21.44140625" bestFit="1" customWidth="1"/>
     <col min="2" max="2" width="23.6640625" customWidth="1"/>
@@ -1117,115 +1135,115 @@
     <col min="9" max="9" width="11.5546875" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:8" ht="18" x14ac:dyDescent="0.45">
-      <c r="A1" s="20" t="s">
+    <row r="1" spans="1:8" ht="18">
+      <c r="A1" s="18" t="s">
         <v>0</v>
       </c>
       <c r="B1" s="6" t="s">
         <v>51</v>
       </c>
-      <c r="G1" s="31" t="s">
-        <v>141</v>
+      <c r="G1" s="28" t="s">
+        <v>139</v>
       </c>
       <c r="H1" s="6" t="s">
-        <v>140</v>
-      </c>
-    </row>
-    <row r="2" spans="1:8" x14ac:dyDescent="0.3">
-      <c r="A2" s="20" t="s">
+        <v>138</v>
+      </c>
+    </row>
+    <row r="2" spans="1:8">
+      <c r="A2" s="18" t="s">
         <v>47</v>
       </c>
       <c r="B2" s="6" t="s">
-        <v>120</v>
-      </c>
-      <c r="G2" s="31" t="s">
-        <v>138</v>
+        <v>118</v>
+      </c>
+      <c r="G2" s="28" t="s">
+        <v>136</v>
       </c>
       <c r="H2" s="6" t="s">
-        <v>120</v>
-      </c>
-    </row>
-    <row r="3" spans="1:8" x14ac:dyDescent="0.3">
-      <c r="A3" s="20" t="s">
-        <v>132</v>
+        <v>118</v>
+      </c>
+    </row>
+    <row r="3" spans="1:8">
+      <c r="A3" s="18" t="s">
+        <v>130</v>
       </c>
       <c r="B3" s="6">
         <v>92711</v>
       </c>
-      <c r="G3" s="31" t="s">
-        <v>139</v>
+      <c r="G3" s="28" t="s">
+        <v>137</v>
       </c>
       <c r="H3" s="6">
         <v>42952</v>
       </c>
     </row>
-    <row r="4" spans="1:8" x14ac:dyDescent="0.3">
-      <c r="D4" s="17"/>
-      <c r="E4" s="17"/>
+    <row r="4" spans="1:8">
+      <c r="D4" s="15"/>
+      <c r="E4" s="15"/>
       <c r="F4" s="6"/>
     </row>
-    <row r="5" spans="1:8" ht="21" x14ac:dyDescent="0.4">
-      <c r="A5" s="13" t="s">
+    <row r="5" spans="1:8" ht="20">
+      <c r="A5" s="30" t="s">
         <v>1</v>
       </c>
-      <c r="B5" s="14"/>
-      <c r="C5" s="14"/>
-      <c r="D5" s="14"/>
-      <c r="E5" s="14"/>
-      <c r="F5" s="14"/>
-      <c r="G5" s="14"/>
-      <c r="H5" s="14"/>
-    </row>
-    <row r="6" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="B5" s="31"/>
+      <c r="C5" s="31"/>
+      <c r="D5" s="31"/>
+      <c r="E5" s="31"/>
+      <c r="F5" s="31"/>
+      <c r="G5" s="31"/>
+      <c r="H5" s="31"/>
+    </row>
+    <row r="6" spans="1:8">
       <c r="A6" t="s">
-        <v>164</v>
-      </c>
-    </row>
-    <row r="7" spans="1:8" x14ac:dyDescent="0.3">
+        <v>162</v>
+      </c>
+    </row>
+    <row r="7" spans="1:8">
       <c r="A7" t="s">
-        <v>163</v>
-      </c>
-    </row>
-    <row r="8" spans="1:8" x14ac:dyDescent="0.3">
+        <v>161</v>
+      </c>
+    </row>
+    <row r="8" spans="1:8">
       <c r="A8" s="1" t="s">
-        <v>144</v>
+        <v>142</v>
       </c>
       <c r="C8" s="8" t="s">
-        <v>135</v>
-      </c>
-    </row>
-    <row r="9" spans="1:8" s="1" customFormat="1" x14ac:dyDescent="0.3">
-      <c r="A9" s="15" t="s">
+        <v>133</v>
+      </c>
+    </row>
+    <row r="9" spans="1:8" s="1" customFormat="1">
+      <c r="A9" s="13" t="s">
         <v>2</v>
       </c>
-      <c r="B9" s="15" t="s">
+      <c r="B9" s="13" t="s">
         <v>49</v>
       </c>
-      <c r="C9" s="15" t="s">
-        <v>63</v>
-      </c>
-      <c r="D9" s="28" t="s">
-        <v>71</v>
-      </c>
-      <c r="E9" s="28" t="s">
-        <v>157</v>
-      </c>
-      <c r="F9" s="28" t="s">
-        <v>130</v>
-      </c>
-      <c r="G9" s="28" t="s">
+      <c r="C9" s="13" t="s">
+        <v>61</v>
+      </c>
+      <c r="D9" s="25" t="s">
+        <v>69</v>
+      </c>
+      <c r="E9" s="25" t="s">
+        <v>155</v>
+      </c>
+      <c r="F9" s="25" t="s">
+        <v>128</v>
+      </c>
+      <c r="G9" s="25" t="s">
         <v>4</v>
       </c>
-      <c r="H9" s="29" t="s">
+      <c r="H9" s="26" t="s">
         <v>22</v>
       </c>
     </row>
-    <row r="10" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="10" spans="1:8">
       <c r="A10" s="7"/>
       <c r="B10" s="5" t="s">
-        <v>70</v>
-      </c>
-      <c r="C10" s="16" t="str">
+        <v>68</v>
+      </c>
+      <c r="C10" s="14" t="str">
         <f t="shared" ref="C10:C16" si="0">IF(RIGHT(TRIM(B10),5)="Blank",
      0,
      IF(ISNUMBER(SEARCH("Level",B10)),
@@ -1245,14 +1263,14 @@
         <v>46</v>
       </c>
     </row>
-    <row r="11" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="11" spans="1:8">
       <c r="A11" s="7">
         <v>92012</v>
       </c>
       <c r="B11" s="5" t="s">
         <v>37</v>
       </c>
-      <c r="C11" s="16" t="str">
+      <c r="C11" s="14" t="str">
         <f t="shared" si="0"/>
         <v/>
       </c>
@@ -1268,14 +1286,14 @@
         <v>19</v>
       </c>
     </row>
-    <row r="12" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="12" spans="1:8">
       <c r="A12" s="7">
         <v>92005</v>
       </c>
       <c r="B12" s="5" t="s">
         <v>38</v>
       </c>
-      <c r="C12" s="16" t="str">
+      <c r="C12" s="14" t="str">
         <f t="shared" si="0"/>
         <v/>
       </c>
@@ -1291,14 +1309,14 @@
         <v>16</v>
       </c>
     </row>
-    <row r="13" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="13" spans="1:8">
       <c r="A13" s="7">
         <v>92007</v>
       </c>
       <c r="B13" s="5" t="s">
         <v>39</v>
       </c>
-      <c r="C13" s="16" t="str">
+      <c r="C13" s="14" t="str">
         <f t="shared" si="0"/>
         <v/>
       </c>
@@ -1314,14 +1332,14 @@
         <v>19</v>
       </c>
     </row>
-    <row r="14" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="14" spans="1:8">
       <c r="A14" s="7">
         <v>92008</v>
       </c>
       <c r="B14" s="5" t="s">
         <v>40</v>
       </c>
-      <c r="C14" s="16" t="str">
+      <c r="C14" s="14" t="str">
         <f t="shared" si="0"/>
         <v/>
       </c>
@@ -1337,14 +1355,14 @@
         <v>19</v>
       </c>
     </row>
-    <row r="15" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="15" spans="1:8">
       <c r="A15" s="7">
         <v>92057</v>
       </c>
       <c r="B15" s="5" t="s">
         <v>41</v>
       </c>
-      <c r="C15" s="16" t="str">
+      <c r="C15" s="14" t="str">
         <f t="shared" si="0"/>
         <v/>
       </c>
@@ -1358,14 +1376,14 @@
       </c>
       <c r="H15" s="7"/>
     </row>
-    <row r="16" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="16" spans="1:8">
       <c r="A16" s="7">
         <v>92058</v>
       </c>
       <c r="B16" s="5" t="s">
         <v>42</v>
       </c>
-      <c r="C16" s="16" t="str">
+      <c r="C16" s="14" t="str">
         <f t="shared" si="0"/>
         <v/>
       </c>
@@ -1379,913 +1397,877 @@
       </c>
       <c r="H16" s="7"/>
     </row>
-    <row r="17" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="17" spans="1:8">
       <c r="A17" s="7" t="s">
-        <v>53</v>
+        <v>52</v>
       </c>
       <c r="B17" s="5" t="s">
-        <v>57</v>
-      </c>
-      <c r="C17" s="16">
-        <f>IF(RIGHT(TRIM(B17),5)="Blank",
+        <v>170</v>
+      </c>
+      <c r="C17" s="14" t="str">
+        <f t="shared" ref="C17:C23" si="1">IF(RIGHT(TRIM(B17),5)="Blank",
      0,
      IF(ISNUMBER(SEARCH("Level",B17)),
           RIGHT(TRIM(B17),2),
           ""
      )
 )</f>
-        <v>0</v>
+        <v xml:space="preserve"> 0</v>
       </c>
       <c r="D17" s="9" t="s">
-        <v>137</v>
+        <v>135</v>
       </c>
       <c r="E17" s="9" t="s">
-        <v>158</v>
+        <v>156</v>
       </c>
       <c r="F17" s="9" t="s">
-        <v>136</v>
+        <v>134</v>
       </c>
       <c r="G17" s="9" t="s">
         <v>8</v>
       </c>
       <c r="H17" s="7" t="s">
-        <v>67</v>
-      </c>
-    </row>
-    <row r="18" spans="1:8" x14ac:dyDescent="0.3">
+        <v>65</v>
+      </c>
+    </row>
+    <row r="18" spans="1:8">
       <c r="A18" s="7" t="s">
-        <v>54</v>
+        <v>53</v>
       </c>
       <c r="B18" s="5" t="s">
-        <v>58</v>
-      </c>
-      <c r="C18" s="16" t="str">
-        <f>IF(RIGHT(TRIM(B18),5)="Blank",
-     0,
-     IF(ISNUMBER(SEARCH("Level",B18)),
-          RIGHT(TRIM(B18),2),
-          ""
-     )
-)</f>
+        <v>56</v>
+      </c>
+      <c r="C18" s="14" t="str">
+        <f t="shared" si="1"/>
         <v xml:space="preserve"> 1</v>
       </c>
       <c r="D18" s="9" t="s">
-        <v>137</v>
+        <v>135</v>
       </c>
       <c r="E18" s="9" t="s">
-        <v>158</v>
+        <v>156</v>
       </c>
       <c r="F18" s="9" t="s">
-        <v>136</v>
+        <v>134</v>
       </c>
       <c r="G18" s="9" t="s">
         <v>8</v>
       </c>
       <c r="H18" s="7" t="s">
-        <v>67</v>
-      </c>
-    </row>
-    <row r="19" spans="1:8" x14ac:dyDescent="0.3">
+        <v>65</v>
+      </c>
+    </row>
+    <row r="19" spans="1:8">
       <c r="A19" s="7" t="s">
-        <v>55</v>
+        <v>54</v>
       </c>
       <c r="B19" s="5" t="s">
-        <v>59</v>
-      </c>
-      <c r="C19" s="16" t="str">
-        <f>IF(RIGHT(TRIM(B19),5)="Blank",
-     0,
-     IF(ISNUMBER(SEARCH("Level",B19)),
-          RIGHT(TRIM(B19),2),
-          ""
-     )
-)</f>
+        <v>57</v>
+      </c>
+      <c r="C19" s="14" t="str">
+        <f t="shared" si="1"/>
         <v xml:space="preserve"> 2</v>
       </c>
       <c r="D19" s="9" t="s">
-        <v>137</v>
+        <v>135</v>
       </c>
       <c r="E19" s="9" t="s">
-        <v>158</v>
+        <v>156</v>
       </c>
       <c r="F19" s="9" t="s">
-        <v>136</v>
+        <v>134</v>
       </c>
       <c r="G19" s="9" t="s">
         <v>8</v>
       </c>
       <c r="H19" s="7" t="s">
-        <v>67</v>
-      </c>
-    </row>
-    <row r="20" spans="1:8" x14ac:dyDescent="0.3">
+        <v>65</v>
+      </c>
+    </row>
+    <row r="20" spans="1:8">
       <c r="A20" s="7" t="s">
-        <v>56</v>
+        <v>55</v>
       </c>
       <c r="B20" s="5" t="s">
-        <v>60</v>
-      </c>
-      <c r="C20" s="16" t="str">
-        <f>IF(RIGHT(TRIM(B20),5)="Blank",
-     0,
-     IF(ISNUMBER(SEARCH("Level",B20)),
-          RIGHT(TRIM(B20),2),
-          ""
-     )
-)</f>
+        <v>58</v>
+      </c>
+      <c r="C20" s="14" t="str">
+        <f t="shared" si="1"/>
         <v xml:space="preserve"> 3</v>
       </c>
       <c r="D20" s="9" t="s">
-        <v>137</v>
+        <v>135</v>
       </c>
       <c r="E20" s="9" t="s">
-        <v>158</v>
+        <v>156</v>
       </c>
       <c r="F20" s="9" t="s">
-        <v>136</v>
+        <v>134</v>
       </c>
       <c r="G20" s="9" t="s">
         <v>8</v>
       </c>
       <c r="H20" s="7" t="s">
-        <v>67</v>
-      </c>
-    </row>
-    <row r="21" spans="1:8" x14ac:dyDescent="0.3">
+        <v>65</v>
+      </c>
+    </row>
+    <row r="21" spans="1:8">
       <c r="A21" s="7" t="s">
-        <v>61</v>
+        <v>59</v>
       </c>
       <c r="B21" s="5" t="s">
-        <v>64</v>
-      </c>
-      <c r="C21" s="16" t="str">
-        <f>IF(RIGHT(TRIM(B21),5)="Blank",
-     0,
-     IF(ISNUMBER(SEARCH("Level",B21)),
-          RIGHT(TRIM(B21),2),
-          ""
-     )
-)</f>
+        <v>62</v>
+      </c>
+      <c r="C21" s="14" t="str">
+        <f t="shared" si="1"/>
         <v xml:space="preserve"> I</v>
       </c>
       <c r="D21" s="9" t="s">
-        <v>137</v>
+        <v>135</v>
       </c>
       <c r="E21" s="9" t="s">
-        <v>158</v>
+        <v>156</v>
       </c>
       <c r="F21" s="9" t="s">
-        <v>136</v>
+        <v>134</v>
       </c>
       <c r="G21" s="9" t="s">
         <v>9</v>
       </c>
       <c r="H21" s="7" t="s">
-        <v>67</v>
-      </c>
-    </row>
-    <row r="22" spans="1:8" x14ac:dyDescent="0.3">
+        <v>65</v>
+      </c>
+    </row>
+    <row r="22" spans="1:8">
       <c r="A22" s="7" t="s">
-        <v>62</v>
+        <v>60</v>
       </c>
       <c r="B22" s="5" t="s">
-        <v>65</v>
-      </c>
-      <c r="C22" s="16" t="str">
-        <f>IF(RIGHT(TRIM(B22),5)="Blank",
-     0,
-     IF(ISNUMBER(SEARCH("Level",B22)),
-          RIGHT(TRIM(B22),2),
-          ""
-     )
-)</f>
+        <v>63</v>
+      </c>
+      <c r="C22" s="14" t="str">
+        <f t="shared" si="1"/>
         <v>II</v>
       </c>
       <c r="D22" s="9" t="s">
-        <v>137</v>
+        <v>135</v>
       </c>
       <c r="E22" s="9" t="s">
-        <v>158</v>
+        <v>156</v>
       </c>
       <c r="F22" s="9" t="s">
-        <v>136</v>
+        <v>134</v>
       </c>
       <c r="G22" s="9" t="s">
         <v>9</v>
       </c>
       <c r="H22" s="7" t="s">
+        <v>65</v>
+      </c>
+    </row>
+    <row r="23" spans="1:8">
+      <c r="A23" s="7" t="s">
+        <v>70</v>
+      </c>
+      <c r="B23" s="5" t="s">
         <v>67</v>
       </c>
-    </row>
-    <row r="23" spans="1:8" x14ac:dyDescent="0.3">
-      <c r="A23" s="7" t="s">
-        <v>72</v>
-      </c>
-      <c r="B23" s="5" t="s">
-        <v>69</v>
-      </c>
-      <c r="C23" s="16" t="str">
-        <f>IF(RIGHT(TRIM(B23),5)="Blank",
-     0,
-     IF(ISNUMBER(SEARCH("Level",B23)),
-          RIGHT(TRIM(B23),2),
-          ""
-     )
-)</f>
+      <c r="C23" s="14" t="str">
+        <f t="shared" si="1"/>
         <v/>
       </c>
       <c r="D23" s="9" t="s">
-        <v>137</v>
+        <v>135</v>
       </c>
       <c r="E23" s="9" t="s">
-        <v>158</v>
+        <v>156</v>
       </c>
       <c r="F23" s="9" t="s">
-        <v>136</v>
+        <v>134</v>
       </c>
       <c r="G23" s="9" t="s">
-        <v>66</v>
+        <v>64</v>
       </c>
       <c r="H23" s="7" t="s">
         <v>19</v>
       </c>
     </row>
-    <row r="24" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="24" spans="1:8">
       <c r="A24" s="7"/>
       <c r="B24" s="5"/>
-      <c r="C24" s="16"/>
+      <c r="C24" s="14"/>
       <c r="D24" s="9" t="s">
-        <v>154</v>
+        <v>152</v>
       </c>
       <c r="E24" s="9" t="s">
-        <v>159</v>
+        <v>157</v>
       </c>
       <c r="F24" s="9" t="s">
-        <v>153</v>
+        <v>151</v>
       </c>
       <c r="G24" s="9"/>
       <c r="H24" s="7"/>
     </row>
-    <row r="25" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="25" spans="1:8">
       <c r="A25" s="7"/>
       <c r="B25" s="5"/>
-      <c r="C25" s="16"/>
+      <c r="C25" s="14"/>
       <c r="D25" s="9" t="s">
-        <v>156</v>
+        <v>154</v>
       </c>
       <c r="E25" s="9" t="s">
-        <v>160</v>
+        <v>158</v>
       </c>
       <c r="F25" s="9" t="s">
-        <v>155</v>
+        <v>153</v>
       </c>
       <c r="G25" s="9"/>
       <c r="H25" s="7"/>
     </row>
-    <row r="26" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="26" spans="1:8">
       <c r="A26" s="7"/>
       <c r="B26" s="5"/>
-      <c r="C26" s="16"/>
+      <c r="C26" s="14"/>
       <c r="D26" s="9"/>
       <c r="E26" s="9"/>
       <c r="F26" s="9"/>
       <c r="G26" s="9"/>
       <c r="H26" s="7"/>
     </row>
-    <row r="27" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="27" spans="1:8">
       <c r="A27" s="7"/>
       <c r="B27" s="5"/>
-      <c r="C27" s="16"/>
+      <c r="C27" s="14"/>
       <c r="D27" s="9"/>
       <c r="E27" s="9"/>
       <c r="F27" s="9"/>
       <c r="G27" s="9"/>
       <c r="H27" s="7"/>
     </row>
-    <row r="28" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="28" spans="1:8">
       <c r="A28" s="7"/>
       <c r="B28" s="5"/>
-      <c r="C28" s="16"/>
+      <c r="C28" s="14"/>
       <c r="D28" s="9"/>
       <c r="E28" s="9"/>
       <c r="F28" s="9"/>
       <c r="G28" s="9"/>
       <c r="H28" s="7"/>
     </row>
-    <row r="29" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="29" spans="1:8">
       <c r="A29" s="7"/>
       <c r="B29" s="5"/>
-      <c r="C29" s="16"/>
+      <c r="C29" s="14"/>
       <c r="D29" s="9"/>
       <c r="E29" s="9"/>
       <c r="F29" s="9"/>
       <c r="G29" s="9"/>
       <c r="H29" s="7"/>
     </row>
-    <row r="30" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="30" spans="1:8">
       <c r="A30" s="7"/>
       <c r="B30" s="5"/>
-      <c r="C30" s="16"/>
+      <c r="C30" s="14"/>
       <c r="D30" s="9"/>
       <c r="E30" s="9"/>
       <c r="F30" s="9"/>
       <c r="G30" s="9"/>
       <c r="H30" s="7"/>
     </row>
-    <row r="31" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="31" spans="1:8">
       <c r="A31" s="7"/>
       <c r="B31" s="5"/>
-      <c r="C31" s="16"/>
+      <c r="C31" s="14"/>
       <c r="D31" s="9"/>
       <c r="E31" s="9"/>
       <c r="F31" s="9"/>
       <c r="G31" s="9"/>
       <c r="H31" s="7"/>
     </row>
-    <row r="32" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="32" spans="1:8">
       <c r="A32" s="7"/>
       <c r="B32" s="5"/>
-      <c r="C32" s="16"/>
+      <c r="C32" s="14"/>
       <c r="D32" s="9"/>
       <c r="E32" s="9"/>
       <c r="F32" s="9"/>
       <c r="G32" s="9"/>
       <c r="H32" s="7"/>
     </row>
-    <row r="33" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="33" spans="1:8">
       <c r="A33" s="7"/>
       <c r="B33" s="5"/>
-      <c r="C33" s="16"/>
+      <c r="C33" s="14"/>
       <c r="D33" s="9"/>
       <c r="E33" s="9"/>
       <c r="F33" s="9"/>
       <c r="G33" s="9"/>
       <c r="H33" s="7"/>
     </row>
-    <row r="34" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="34" spans="1:8">
       <c r="A34" s="7"/>
       <c r="B34" s="5"/>
-      <c r="C34" s="16"/>
+      <c r="C34" s="14"/>
       <c r="D34" s="9"/>
       <c r="E34" s="9"/>
       <c r="F34" s="9"/>
       <c r="G34" s="9"/>
       <c r="H34" s="7"/>
     </row>
-    <row r="35" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="35" spans="1:8">
       <c r="A35" s="7"/>
       <c r="B35" s="5"/>
-      <c r="C35" s="16"/>
+      <c r="C35" s="14"/>
       <c r="D35" s="9"/>
       <c r="E35" s="9"/>
       <c r="F35" s="9"/>
       <c r="G35" s="9"/>
       <c r="H35" s="7"/>
     </row>
-    <row r="36" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="36" spans="1:8">
       <c r="A36" s="7"/>
       <c r="B36" s="5"/>
-      <c r="C36" s="16"/>
+      <c r="C36" s="14"/>
       <c r="D36" s="9"/>
       <c r="E36" s="9"/>
       <c r="F36" s="9"/>
       <c r="G36" s="9"/>
       <c r="H36" s="7"/>
     </row>
-    <row r="37" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="37" spans="1:8">
       <c r="A37" s="7"/>
       <c r="B37" s="5"/>
-      <c r="C37" s="16"/>
+      <c r="C37" s="14"/>
       <c r="D37" s="9"/>
       <c r="E37" s="9"/>
       <c r="F37" s="9"/>
       <c r="G37" s="9"/>
       <c r="H37" s="7"/>
     </row>
-    <row r="38" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="38" spans="1:8">
       <c r="A38" s="7"/>
       <c r="B38" s="5"/>
-      <c r="C38" s="16"/>
+      <c r="C38" s="14"/>
       <c r="D38" s="9"/>
       <c r="E38" s="9"/>
       <c r="F38" s="9"/>
       <c r="G38" s="9"/>
       <c r="H38" s="7"/>
     </row>
-    <row r="39" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="39" spans="1:8">
       <c r="A39" s="7"/>
       <c r="B39" s="5"/>
-      <c r="C39" s="16"/>
+      <c r="C39" s="14"/>
       <c r="D39" s="9"/>
       <c r="E39" s="9"/>
       <c r="F39" s="9"/>
       <c r="G39" s="9"/>
       <c r="H39" s="7"/>
     </row>
-    <row r="40" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="40" spans="1:8">
       <c r="A40" s="7"/>
       <c r="B40" s="5"/>
-      <c r="C40" s="16"/>
+      <c r="C40" s="14"/>
       <c r="D40" s="9"/>
       <c r="E40" s="9"/>
       <c r="F40" s="9"/>
       <c r="G40" s="9"/>
       <c r="H40" s="7"/>
     </row>
-    <row r="41" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="41" spans="1:8">
       <c r="A41" s="7"/>
       <c r="B41" s="5"/>
-      <c r="C41" s="16"/>
+      <c r="C41" s="14"/>
       <c r="D41" s="9"/>
       <c r="E41" s="9"/>
       <c r="F41" s="9"/>
       <c r="G41" s="9"/>
       <c r="H41" s="7"/>
     </row>
-    <row r="42" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="42" spans="1:8">
       <c r="A42" s="7"/>
       <c r="B42" s="5"/>
-      <c r="C42" s="16"/>
+      <c r="C42" s="14"/>
       <c r="D42" s="9"/>
       <c r="E42" s="9"/>
       <c r="F42" s="9"/>
       <c r="G42" s="9"/>
       <c r="H42" s="7"/>
     </row>
-    <row r="43" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="43" spans="1:8">
       <c r="A43" s="7"/>
       <c r="B43" s="5"/>
-      <c r="C43" s="16"/>
+      <c r="C43" s="14"/>
       <c r="D43" s="9"/>
       <c r="E43" s="9"/>
       <c r="F43" s="9"/>
       <c r="G43" s="9"/>
       <c r="H43" s="7"/>
     </row>
-    <row r="44" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="44" spans="1:8">
       <c r="A44" s="7"/>
       <c r="B44" s="5"/>
-      <c r="C44" s="16"/>
+      <c r="C44" s="14"/>
       <c r="D44" s="9"/>
       <c r="E44" s="9"/>
       <c r="F44" s="9"/>
       <c r="G44" s="9"/>
       <c r="H44" s="7"/>
     </row>
-    <row r="45" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="45" spans="1:8">
       <c r="A45" s="7"/>
       <c r="B45" s="5"/>
-      <c r="C45" s="16"/>
+      <c r="C45" s="14"/>
       <c r="D45" s="9"/>
       <c r="E45" s="9"/>
       <c r="F45" s="9"/>
       <c r="G45" s="9"/>
       <c r="H45" s="7"/>
     </row>
-    <row r="46" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="46" spans="1:8">
       <c r="A46" s="7"/>
       <c r="B46" s="5"/>
-      <c r="C46" s="16"/>
+      <c r="C46" s="14"/>
       <c r="D46" s="9"/>
       <c r="E46" s="9"/>
       <c r="F46" s="9"/>
       <c r="G46" s="9"/>
       <c r="H46" s="7"/>
     </row>
-    <row r="47" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="47" spans="1:8">
       <c r="A47" s="7"/>
       <c r="B47" s="5"/>
-      <c r="C47" s="16"/>
+      <c r="C47" s="14"/>
       <c r="D47" s="9"/>
       <c r="E47" s="9"/>
       <c r="F47" s="9"/>
       <c r="G47" s="9"/>
       <c r="H47" s="7"/>
     </row>
-    <row r="48" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="48" spans="1:8">
       <c r="A48" s="7"/>
       <c r="B48" s="5"/>
-      <c r="C48" s="16"/>
+      <c r="C48" s="14"/>
       <c r="D48" s="9"/>
       <c r="E48" s="9"/>
       <c r="F48" s="9"/>
       <c r="G48" s="9"/>
       <c r="H48" s="7"/>
     </row>
-    <row r="49" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="49" spans="1:8">
       <c r="A49" s="7"/>
       <c r="B49" s="5"/>
-      <c r="C49" s="16"/>
+      <c r="C49" s="14"/>
       <c r="D49" s="9"/>
       <c r="E49" s="9"/>
       <c r="F49" s="9"/>
       <c r="G49" s="9"/>
       <c r="H49" s="7"/>
     </row>
-    <row r="50" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="50" spans="1:8">
       <c r="A50" s="7"/>
       <c r="B50" s="5"/>
-      <c r="C50" s="16"/>
+      <c r="C50" s="14"/>
       <c r="D50" s="9"/>
       <c r="E50" s="9"/>
       <c r="F50" s="9"/>
       <c r="G50" s="9"/>
       <c r="H50" s="7"/>
     </row>
-    <row r="51" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="51" spans="1:8">
       <c r="A51" s="7"/>
       <c r="B51" s="5"/>
-      <c r="C51" s="16"/>
+      <c r="C51" s="14"/>
       <c r="D51" s="9"/>
       <c r="E51" s="9"/>
       <c r="F51" s="9"/>
       <c r="G51" s="9"/>
       <c r="H51" s="7"/>
     </row>
-    <row r="52" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="52" spans="1:8">
       <c r="A52" s="7"/>
       <c r="B52" s="5"/>
-      <c r="C52" s="16"/>
+      <c r="C52" s="14"/>
       <c r="D52" s="9"/>
       <c r="E52" s="9"/>
       <c r="F52" s="9"/>
       <c r="G52" s="9"/>
       <c r="H52" s="7"/>
     </row>
-    <row r="53" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="53" spans="1:8">
       <c r="A53" s="7"/>
       <c r="B53" s="5"/>
-      <c r="C53" s="16"/>
+      <c r="C53" s="14"/>
       <c r="D53" s="9"/>
       <c r="E53" s="9"/>
       <c r="F53" s="9"/>
       <c r="G53" s="9"/>
       <c r="H53" s="7"/>
     </row>
-    <row r="54" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="54" spans="1:8">
       <c r="A54" s="7"/>
       <c r="B54" s="5"/>
-      <c r="C54" s="16"/>
+      <c r="C54" s="14"/>
       <c r="D54" s="9"/>
       <c r="E54" s="9"/>
       <c r="F54" s="9"/>
       <c r="G54" s="9"/>
       <c r="H54" s="7"/>
     </row>
-    <row r="55" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="55" spans="1:8">
       <c r="A55" s="7"/>
       <c r="B55" s="5"/>
-      <c r="C55" s="16"/>
+      <c r="C55" s="14"/>
       <c r="D55" s="9"/>
       <c r="E55" s="9"/>
       <c r="F55" s="9"/>
       <c r="G55" s="9"/>
       <c r="H55" s="7"/>
     </row>
-    <row r="56" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="56" spans="1:8">
       <c r="A56" s="7"/>
       <c r="B56" s="5"/>
-      <c r="C56" s="16"/>
+      <c r="C56" s="14"/>
       <c r="D56" s="9"/>
       <c r="E56" s="9"/>
       <c r="F56" s="9"/>
       <c r="G56" s="9"/>
       <c r="H56" s="7"/>
     </row>
-    <row r="57" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="57" spans="1:8">
       <c r="A57" s="7"/>
       <c r="B57" s="5"/>
-      <c r="C57" s="16"/>
+      <c r="C57" s="14"/>
       <c r="D57" s="9"/>
       <c r="E57" s="9"/>
       <c r="F57" s="9"/>
       <c r="G57" s="9"/>
       <c r="H57" s="7"/>
     </row>
-    <row r="58" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="58" spans="1:8">
       <c r="A58" s="7"/>
       <c r="B58" s="5"/>
-      <c r="C58" s="16"/>
+      <c r="C58" s="14"/>
       <c r="D58" s="9"/>
       <c r="E58" s="9"/>
       <c r="F58" s="9"/>
       <c r="G58" s="9"/>
       <c r="H58" s="7"/>
     </row>
-    <row r="59" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="59" spans="1:8">
       <c r="A59" s="7"/>
       <c r="B59" s="5"/>
-      <c r="C59" s="16"/>
+      <c r="C59" s="14"/>
       <c r="D59" s="9"/>
       <c r="E59" s="9"/>
       <c r="F59" s="9"/>
       <c r="G59" s="9"/>
       <c r="H59" s="7"/>
     </row>
-    <row r="60" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="60" spans="1:8">
       <c r="A60" s="7"/>
       <c r="B60" s="5"/>
-      <c r="C60" s="16"/>
+      <c r="C60" s="14"/>
       <c r="D60" s="9"/>
       <c r="E60" s="9"/>
       <c r="F60" s="9"/>
       <c r="G60" s="9"/>
       <c r="H60" s="7"/>
     </row>
-    <row r="61" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="61" spans="1:8">
       <c r="A61" s="7"/>
       <c r="B61" s="5"/>
-      <c r="C61" s="16"/>
+      <c r="C61" s="14"/>
       <c r="D61" s="9"/>
       <c r="E61" s="9"/>
       <c r="F61" s="9"/>
       <c r="G61" s="9"/>
       <c r="H61" s="7"/>
     </row>
-    <row r="62" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="62" spans="1:8">
       <c r="A62" s="7"/>
       <c r="B62" s="5"/>
-      <c r="C62" s="16"/>
+      <c r="C62" s="14"/>
       <c r="D62" s="9"/>
       <c r="E62" s="9"/>
       <c r="F62" s="9"/>
       <c r="G62" s="9"/>
       <c r="H62" s="7"/>
     </row>
-    <row r="63" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="63" spans="1:8">
       <c r="A63" s="7"/>
       <c r="B63" s="5"/>
-      <c r="C63" s="16"/>
+      <c r="C63" s="14"/>
       <c r="D63" s="9"/>
       <c r="E63" s="9"/>
       <c r="F63" s="9"/>
       <c r="G63" s="9"/>
       <c r="H63" s="7"/>
     </row>
-    <row r="64" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="64" spans="1:8">
       <c r="A64" s="7"/>
       <c r="B64" s="5"/>
-      <c r="C64" s="16"/>
+      <c r="C64" s="14"/>
       <c r="D64" s="9"/>
       <c r="E64" s="9"/>
       <c r="F64" s="9"/>
       <c r="G64" s="9"/>
       <c r="H64" s="7"/>
     </row>
-    <row r="65" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="65" spans="1:8">
       <c r="A65" s="7"/>
       <c r="B65" s="5"/>
-      <c r="C65" s="16"/>
+      <c r="C65" s="14"/>
       <c r="D65" s="9"/>
       <c r="E65" s="9"/>
       <c r="F65" s="9"/>
       <c r="G65" s="9"/>
       <c r="H65" s="7"/>
     </row>
-    <row r="66" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="66" spans="1:8">
       <c r="A66" s="7"/>
       <c r="B66" s="5"/>
-      <c r="C66" s="16"/>
+      <c r="C66" s="14"/>
       <c r="D66" s="9"/>
       <c r="E66" s="9"/>
       <c r="F66" s="9"/>
       <c r="G66" s="9"/>
       <c r="H66" s="7"/>
     </row>
-    <row r="67" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="67" spans="1:8">
       <c r="A67" s="7"/>
       <c r="B67" s="5"/>
-      <c r="C67" s="16"/>
+      <c r="C67" s="14"/>
       <c r="D67" s="9"/>
       <c r="E67" s="9"/>
       <c r="F67" s="9"/>
       <c r="G67" s="9"/>
       <c r="H67" s="7"/>
     </row>
-    <row r="68" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="68" spans="1:8">
       <c r="A68" s="7"/>
       <c r="B68" s="5"/>
-      <c r="C68" s="16"/>
+      <c r="C68" s="14"/>
       <c r="D68" s="9"/>
       <c r="E68" s="9"/>
       <c r="F68" s="9"/>
       <c r="G68" s="9"/>
       <c r="H68" s="7"/>
     </row>
-    <row r="69" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="69" spans="1:8">
       <c r="A69" s="7"/>
       <c r="B69" s="5"/>
-      <c r="C69" s="16"/>
+      <c r="C69" s="14"/>
       <c r="D69" s="9"/>
       <c r="E69" s="9"/>
       <c r="F69" s="9"/>
       <c r="G69" s="9"/>
       <c r="H69" s="7"/>
     </row>
-    <row r="70" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="70" spans="1:8">
       <c r="A70" s="7"/>
       <c r="B70" s="5"/>
-      <c r="C70" s="16"/>
+      <c r="C70" s="14"/>
       <c r="D70" s="9"/>
       <c r="E70" s="9"/>
       <c r="F70" s="9"/>
       <c r="G70" s="9"/>
       <c r="H70" s="7"/>
     </row>
-    <row r="71" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="71" spans="1:8">
       <c r="A71" s="7"/>
       <c r="B71" s="5"/>
-      <c r="C71" s="16"/>
+      <c r="C71" s="14"/>
       <c r="D71" s="9"/>
       <c r="E71" s="9"/>
       <c r="F71" s="9"/>
       <c r="G71" s="9"/>
       <c r="H71" s="7"/>
     </row>
-    <row r="72" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="72" spans="1:8">
       <c r="A72" s="7"/>
       <c r="B72" s="5"/>
-      <c r="C72" s="16"/>
+      <c r="C72" s="14"/>
       <c r="D72" s="9"/>
       <c r="E72" s="9"/>
       <c r="F72" s="9"/>
       <c r="G72" s="9"/>
       <c r="H72" s="7"/>
     </row>
-    <row r="73" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="73" spans="1:8">
       <c r="A73" s="7"/>
       <c r="B73" s="5"/>
-      <c r="C73" s="16"/>
+      <c r="C73" s="14"/>
       <c r="D73" s="9"/>
       <c r="E73" s="9"/>
       <c r="F73" s="9"/>
       <c r="G73" s="9"/>
       <c r="H73" s="7"/>
     </row>
-    <row r="74" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="74" spans="1:8">
       <c r="A74" s="7"/>
       <c r="B74" s="5"/>
-      <c r="C74" s="16"/>
+      <c r="C74" s="14"/>
       <c r="D74" s="9"/>
       <c r="E74" s="9"/>
       <c r="F74" s="9"/>
       <c r="G74" s="9"/>
       <c r="H74" s="7"/>
     </row>
-    <row r="75" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="75" spans="1:8">
       <c r="A75" s="7"/>
       <c r="B75" s="5"/>
-      <c r="C75" s="16"/>
+      <c r="C75" s="14"/>
       <c r="D75" s="9"/>
       <c r="E75" s="9"/>
       <c r="F75" s="9"/>
       <c r="G75" s="9"/>
       <c r="H75" s="7"/>
     </row>
-    <row r="76" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="76" spans="1:8">
       <c r="A76" s="7"/>
       <c r="B76" s="5"/>
-      <c r="C76" s="16"/>
+      <c r="C76" s="14"/>
       <c r="D76" s="9"/>
       <c r="E76" s="9"/>
       <c r="F76" s="9"/>
       <c r="G76" s="9"/>
       <c r="H76" s="7"/>
     </row>
-    <row r="77" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="77" spans="1:8">
       <c r="A77" s="7"/>
       <c r="B77" s="5"/>
-      <c r="C77" s="16"/>
+      <c r="C77" s="14"/>
       <c r="D77" s="9"/>
       <c r="E77" s="9"/>
       <c r="F77" s="9"/>
       <c r="G77" s="9"/>
       <c r="H77" s="7"/>
     </row>
-    <row r="78" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="78" spans="1:8">
       <c r="A78" s="7"/>
       <c r="B78" s="5"/>
-      <c r="C78" s="16"/>
+      <c r="C78" s="14"/>
       <c r="D78" s="9"/>
       <c r="E78" s="9"/>
       <c r="F78" s="9"/>
       <c r="G78" s="9"/>
       <c r="H78" s="7"/>
     </row>
-    <row r="79" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="79" spans="1:8">
       <c r="A79" s="7"/>
       <c r="B79" s="5"/>
-      <c r="C79" s="16"/>
+      <c r="C79" s="14"/>
       <c r="D79" s="9"/>
       <c r="E79" s="9"/>
       <c r="F79" s="9"/>
       <c r="G79" s="9"/>
       <c r="H79" s="7"/>
     </row>
-    <row r="80" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="80" spans="1:8">
       <c r="A80" s="7"/>
       <c r="B80" s="5"/>
-      <c r="C80" s="16"/>
+      <c r="C80" s="14"/>
       <c r="D80" s="9"/>
       <c r="E80" s="9"/>
       <c r="F80" s="9"/>
       <c r="G80" s="9"/>
       <c r="H80" s="7"/>
     </row>
-    <row r="81" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="81" spans="1:8">
       <c r="A81" s="7"/>
       <c r="B81" s="5"/>
-      <c r="C81" s="16"/>
+      <c r="C81" s="14"/>
       <c r="D81" s="9"/>
       <c r="E81" s="9"/>
       <c r="F81" s="9"/>
       <c r="G81" s="9"/>
       <c r="H81" s="7"/>
     </row>
-    <row r="82" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="82" spans="1:8">
       <c r="A82" s="7"/>
       <c r="B82" s="5"/>
-      <c r="C82" s="16"/>
+      <c r="C82" s="14"/>
       <c r="D82" s="9"/>
       <c r="E82" s="9"/>
       <c r="F82" s="9"/>
       <c r="G82" s="9"/>
       <c r="H82" s="7"/>
     </row>
-    <row r="83" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="83" spans="1:8">
       <c r="A83" s="7"/>
       <c r="B83" s="5"/>
-      <c r="C83" s="16"/>
+      <c r="C83" s="14"/>
       <c r="D83" s="9"/>
       <c r="E83" s="9"/>
       <c r="F83" s="9"/>
       <c r="G83" s="9"/>
       <c r="H83" s="7"/>
     </row>
-    <row r="84" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="84" spans="1:8">
       <c r="A84" s="7"/>
       <c r="B84" s="5"/>
-      <c r="C84" s="16"/>
+      <c r="C84" s="14"/>
       <c r="D84" s="9"/>
       <c r="E84" s="9"/>
       <c r="F84" s="9"/>
       <c r="G84" s="9"/>
       <c r="H84" s="7"/>
     </row>
-    <row r="85" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="85" spans="1:8">
       <c r="A85" s="7"/>
       <c r="B85" s="5"/>
-      <c r="C85" s="16"/>
+      <c r="C85" s="14"/>
       <c r="D85" s="9"/>
       <c r="E85" s="9"/>
       <c r="F85" s="9"/>
       <c r="G85" s="9"/>
       <c r="H85" s="7"/>
     </row>
-    <row r="86" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="86" spans="1:8">
       <c r="A86" s="7"/>
       <c r="B86" s="5"/>
-      <c r="C86" s="16"/>
+      <c r="C86" s="14"/>
       <c r="D86" s="9"/>
       <c r="E86" s="9"/>
       <c r="F86" s="9"/>
       <c r="G86" s="9"/>
       <c r="H86" s="7"/>
     </row>
-    <row r="87" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="87" spans="1:8">
       <c r="A87" s="7"/>
       <c r="B87" s="5"/>
-      <c r="C87" s="16"/>
+      <c r="C87" s="14"/>
       <c r="D87" s="9"/>
       <c r="E87" s="9"/>
       <c r="F87" s="9"/>
       <c r="G87" s="9"/>
       <c r="H87" s="7"/>
     </row>
-    <row r="88" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="88" spans="1:8">
       <c r="A88" s="7"/>
       <c r="B88" s="5"/>
-      <c r="C88" s="16"/>
+      <c r="C88" s="14"/>
       <c r="D88" s="9"/>
       <c r="E88" s="9"/>
       <c r="F88" s="9"/>
       <c r="G88" s="9"/>
       <c r="H88" s="7"/>
     </row>
-    <row r="89" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="89" spans="1:8">
       <c r="A89" s="7"/>
       <c r="B89" s="5"/>
-      <c r="C89" s="16"/>
+      <c r="C89" s="14"/>
       <c r="D89" s="9"/>
       <c r="E89" s="9"/>
       <c r="F89" s="9"/>
       <c r="G89" s="9"/>
       <c r="H89" s="7"/>
     </row>
-    <row r="90" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="90" spans="1:8">
       <c r="A90" s="7"/>
       <c r="B90" s="5"/>
-      <c r="C90" s="16"/>
+      <c r="C90" s="14"/>
       <c r="D90" s="9"/>
       <c r="E90" s="9"/>
       <c r="F90" s="9"/>
@@ -2322,7 +2304,7 @@
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{72F6DE2F-6547-4E5F-AEF9-A3AA2857B06F}">
   <dimension ref="A5:F32"/>
-  <sheetFormatPr baseColWidth="10" defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
+  <sheetFormatPr baseColWidth="10" defaultRowHeight="13.7"/>
   <cols>
     <col min="1" max="1" width="12.5546875" customWidth="1"/>
     <col min="2" max="2" width="22.5546875" customWidth="1"/>
@@ -2331,56 +2313,56 @@
     <col min="5" max="5" width="12.44140625" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="5" spans="1:6" ht="21" x14ac:dyDescent="0.4">
-      <c r="A5" s="13" t="s">
+    <row r="5" spans="1:6" ht="20">
+      <c r="A5" s="30" t="s">
         <v>23</v>
       </c>
-      <c r="B5" s="14"/>
-      <c r="C5" s="14"/>
-      <c r="D5" s="14"/>
-      <c r="E5" s="14"/>
-      <c r="F5" s="14"/>
-    </row>
-    <row r="6" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="B5" s="31"/>
+      <c r="C5" s="31"/>
+      <c r="D5" s="31"/>
+      <c r="E5" s="31"/>
+      <c r="F5" s="31"/>
+    </row>
+    <row r="6" spans="1:6">
       <c r="A6" t="s">
         <v>36</v>
       </c>
     </row>
-    <row r="8" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="8" spans="1:6">
       <c r="A8" s="1" t="s">
-        <v>148</v>
-      </c>
-      <c r="D8" s="21" t="s">
+        <v>146</v>
+      </c>
+      <c r="D8" s="19" t="s">
         <v>26</v>
       </c>
-      <c r="E8" s="22" t="s">
-        <v>128</v>
-      </c>
-      <c r="F8" s="22"/>
-    </row>
-    <row r="9" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="E8" s="32" t="s">
+        <v>126</v>
+      </c>
+      <c r="F8" s="32"/>
+    </row>
+    <row r="9" spans="1:6">
       <c r="A9" s="11" t="s">
         <v>24</v>
       </c>
       <c r="B9" s="11" t="s">
+        <v>120</v>
+      </c>
+      <c r="C9" s="11" t="s">
+        <v>121</v>
+      </c>
+      <c r="D9" s="11" t="s">
+        <v>125</v>
+      </c>
+      <c r="E9" s="11" t="s">
         <v>122</v>
       </c>
-      <c r="C9" s="11" t="s">
-        <v>123</v>
-      </c>
-      <c r="D9" s="11" t="s">
-        <v>127</v>
-      </c>
-      <c r="E9" s="11" t="s">
+      <c r="F9" s="11" t="s">
         <v>124</v>
       </c>
-      <c r="F9" s="11" t="s">
-        <v>126</v>
-      </c>
-    </row>
-    <row r="10" spans="1:6" x14ac:dyDescent="0.3">
+    </row>
+    <row r="10" spans="1:6">
       <c r="A10" s="5" t="s">
-        <v>133</v>
+        <v>131</v>
       </c>
       <c r="B10" s="5" t="s">
         <v>50</v>
@@ -2394,12 +2376,12 @@
       <c r="E10" s="5"/>
       <c r="F10" s="5"/>
     </row>
-    <row r="11" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="11" spans="1:6">
       <c r="A11" s="5" t="s">
-        <v>134</v>
+        <v>132</v>
       </c>
       <c r="B11" s="5" t="s">
-        <v>58</v>
+        <v>56</v>
       </c>
       <c r="C11" s="5" t="s">
         <v>41</v>
@@ -2410,12 +2392,12 @@
       <c r="E11" s="5"/>
       <c r="F11" s="5"/>
     </row>
-    <row r="12" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="12" spans="1:6">
       <c r="A12" s="5" t="s">
-        <v>134</v>
+        <v>132</v>
       </c>
       <c r="B12" s="5" t="s">
-        <v>59</v>
+        <v>57</v>
       </c>
       <c r="C12" s="5" t="s">
         <v>41</v>
@@ -2426,12 +2408,12 @@
       <c r="E12" s="5"/>
       <c r="F12" s="5"/>
     </row>
-    <row r="13" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="13" spans="1:6">
       <c r="A13" s="5" t="s">
-        <v>134</v>
+        <v>132</v>
       </c>
       <c r="B13" s="5" t="s">
-        <v>60</v>
+        <v>58</v>
       </c>
       <c r="C13" s="5" t="s">
         <v>41</v>
@@ -2442,12 +2424,12 @@
       <c r="E13" s="5"/>
       <c r="F13" s="5"/>
     </row>
-    <row r="14" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="14" spans="1:6">
       <c r="A14" s="5" t="s">
-        <v>134</v>
+        <v>132</v>
       </c>
       <c r="B14" s="5" t="s">
-        <v>64</v>
+        <v>62</v>
       </c>
       <c r="C14" s="5" t="s">
         <v>41</v>
@@ -2458,12 +2440,12 @@
       <c r="E14" s="5"/>
       <c r="F14" s="5"/>
     </row>
-    <row r="15" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="15" spans="1:6">
       <c r="A15" s="5" t="s">
-        <v>134</v>
+        <v>132</v>
       </c>
       <c r="B15" s="5" t="s">
-        <v>65</v>
+        <v>63</v>
       </c>
       <c r="C15" s="5" t="s">
         <v>41</v>
@@ -2474,9 +2456,9 @@
       <c r="E15" s="5"/>
       <c r="F15" s="5"/>
     </row>
-    <row r="16" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="16" spans="1:6">
       <c r="A16" s="5" t="s">
-        <v>133</v>
+        <v>131</v>
       </c>
       <c r="B16" s="5" t="s">
         <v>38</v>
@@ -2490,7 +2472,7 @@
       <c r="E16" s="5"/>
       <c r="F16" s="5"/>
     </row>
-    <row r="17" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="17" spans="1:6">
       <c r="A17" s="5" t="s">
         <v>27</v>
       </c>
@@ -2506,12 +2488,12 @@
         <v>600</v>
       </c>
     </row>
-    <row r="18" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="18" spans="1:6">
       <c r="A18" s="5" t="s">
-        <v>133</v>
+        <v>131</v>
       </c>
       <c r="B18" s="5" t="s">
-        <v>69</v>
+        <v>67</v>
       </c>
       <c r="C18" s="5" t="s">
         <v>41</v>
@@ -2522,7 +2504,7 @@
       <c r="E18" s="5"/>
       <c r="F18" s="5"/>
     </row>
-    <row r="19" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="19" spans="1:6">
       <c r="A19" s="5" t="s">
         <v>27</v>
       </c>
@@ -2538,7 +2520,7 @@
         <v>1000</v>
       </c>
     </row>
-    <row r="20" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="20" spans="1:6">
       <c r="A20" s="5" t="s">
         <v>28</v>
       </c>
@@ -2556,7 +2538,7 @@
         <v>2000</v>
       </c>
     </row>
-    <row r="21" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="21" spans="1:6">
       <c r="A21" s="5" t="s">
         <v>30</v>
       </c>
@@ -2568,7 +2550,7 @@
       <c r="E21" s="5"/>
       <c r="F21" s="5"/>
     </row>
-    <row r="22" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="22" spans="1:6">
       <c r="A22" s="5"/>
       <c r="B22" s="5"/>
       <c r="C22" s="5"/>
@@ -2576,7 +2558,7 @@
       <c r="E22" s="5"/>
       <c r="F22" s="5"/>
     </row>
-    <row r="23" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="23" spans="1:6">
       <c r="A23" s="5"/>
       <c r="B23" s="5"/>
       <c r="C23" s="5"/>
@@ -2584,7 +2566,7 @@
       <c r="E23" s="5"/>
       <c r="F23" s="5"/>
     </row>
-    <row r="24" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="24" spans="1:6">
       <c r="A24" s="5"/>
       <c r="B24" s="5"/>
       <c r="C24" s="5"/>
@@ -2592,7 +2574,7 @@
       <c r="E24" s="5"/>
       <c r="F24" s="5"/>
     </row>
-    <row r="25" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="25" spans="1:6">
       <c r="A25" s="5"/>
       <c r="B25" s="5"/>
       <c r="C25" s="5"/>
@@ -2600,7 +2582,7 @@
       <c r="E25" s="5"/>
       <c r="F25" s="5"/>
     </row>
-    <row r="26" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="26" spans="1:6">
       <c r="A26" s="5"/>
       <c r="B26" s="5"/>
       <c r="C26" s="5"/>
@@ -2608,7 +2590,7 @@
       <c r="E26" s="5"/>
       <c r="F26" s="5"/>
     </row>
-    <row r="27" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="27" spans="1:6">
       <c r="A27" s="5"/>
       <c r="B27" s="5"/>
       <c r="C27" s="5"/>
@@ -2616,7 +2598,7 @@
       <c r="E27" s="5"/>
       <c r="F27" s="5"/>
     </row>
-    <row r="28" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="28" spans="1:6">
       <c r="A28" s="5"/>
       <c r="B28" s="5"/>
       <c r="C28" s="5"/>
@@ -2624,7 +2606,7 @@
       <c r="E28" s="5"/>
       <c r="F28" s="5"/>
     </row>
-    <row r="29" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="29" spans="1:6">
       <c r="A29" s="5"/>
       <c r="B29" s="5"/>
       <c r="C29" s="5"/>
@@ -2632,7 +2614,7 @@
       <c r="E29" s="5"/>
       <c r="F29" s="5"/>
     </row>
-    <row r="30" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="30" spans="1:6">
       <c r="A30" s="5"/>
       <c r="B30" s="5"/>
       <c r="C30" s="5"/>
@@ -2640,7 +2622,7 @@
       <c r="E30" s="5"/>
       <c r="F30" s="5"/>
     </row>
-    <row r="31" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="31" spans="1:6">
       <c r="A31" s="5"/>
       <c r="B31" s="5"/>
       <c r="C31" s="5"/>
@@ -2648,7 +2630,7 @@
       <c r="E31" s="5"/>
       <c r="F31" s="5"/>
     </row>
-    <row r="32" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="32" spans="1:6">
       <c r="A32" s="5"/>
       <c r="B32" s="5"/>
       <c r="C32" s="5"/>
@@ -2722,51 +2704,51 @@
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{122401B3-6997-4364-8643-8369FFFAD0B3}">
   <dimension ref="A5:D16"/>
-  <sheetFormatPr baseColWidth="10" defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
+  <sheetFormatPr baseColWidth="10" defaultRowHeight="13.7"/>
   <cols>
     <col min="1" max="1" width="23.109375" bestFit="1" customWidth="1"/>
     <col min="2" max="2" width="18.88671875" bestFit="1" customWidth="1"/>
     <col min="3" max="4" width="19.21875" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="5" spans="1:4" ht="21" x14ac:dyDescent="0.4">
-      <c r="A5" s="13" t="s">
+    <row r="5" spans="1:4" ht="20">
+      <c r="A5" s="30" t="s">
+        <v>106</v>
+      </c>
+      <c r="B5" s="31"/>
+      <c r="C5" s="31"/>
+      <c r="D5" s="31"/>
+    </row>
+    <row r="6" spans="1:4">
+      <c r="A6" s="12" t="s">
+        <v>127</v>
+      </c>
+    </row>
+    <row r="7" spans="1:4" ht="20">
+      <c r="A7" s="4"/>
+    </row>
+    <row r="8" spans="1:4">
+      <c r="A8" s="1" t="s">
+        <v>146</v>
+      </c>
+    </row>
+    <row r="9" spans="1:4">
+      <c r="A9" s="11" t="s">
+        <v>107</v>
+      </c>
+      <c r="B9" s="11" t="s">
+        <v>115</v>
+      </c>
+      <c r="C9" s="11" t="s">
+        <v>116</v>
+      </c>
+      <c r="D9" s="11" t="s">
+        <v>117</v>
+      </c>
+    </row>
+    <row r="10" spans="1:4">
+      <c r="A10" s="5" t="s">
         <v>108</v>
-      </c>
-      <c r="B5" s="14"/>
-      <c r="C5" s="14"/>
-      <c r="D5" s="14"/>
-    </row>
-    <row r="6" spans="1:4" x14ac:dyDescent="0.3">
-      <c r="A6" s="12" t="s">
-        <v>129</v>
-      </c>
-    </row>
-    <row r="7" spans="1:4" ht="21" x14ac:dyDescent="0.4">
-      <c r="A7" s="4"/>
-    </row>
-    <row r="8" spans="1:4" x14ac:dyDescent="0.3">
-      <c r="A8" s="1" t="s">
-        <v>148</v>
-      </c>
-    </row>
-    <row r="9" spans="1:4" x14ac:dyDescent="0.3">
-      <c r="A9" s="11" t="s">
-        <v>109</v>
-      </c>
-      <c r="B9" s="11" t="s">
-        <v>117</v>
-      </c>
-      <c r="C9" s="11" t="s">
-        <v>118</v>
-      </c>
-      <c r="D9" s="11" t="s">
-        <v>119</v>
-      </c>
-    </row>
-    <row r="10" spans="1:4" x14ac:dyDescent="0.3">
-      <c r="A10" s="5" t="s">
-        <v>110</v>
       </c>
       <c r="B10" s="5">
         <v>100</v>
@@ -2774,9 +2756,9 @@
       <c r="C10" s="5"/>
       <c r="D10" s="5"/>
     </row>
-    <row r="11" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="11" spans="1:4">
       <c r="A11" s="5" t="s">
-        <v>111</v>
+        <v>109</v>
       </c>
       <c r="B11" s="5">
         <v>100</v>
@@ -2784,9 +2766,9 @@
       <c r="C11" s="5"/>
       <c r="D11" s="5"/>
     </row>
-    <row r="12" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="12" spans="1:4">
       <c r="A12" s="5" t="s">
-        <v>112</v>
+        <v>110</v>
       </c>
       <c r="B12" s="5">
         <v>50</v>
@@ -2796,9 +2778,9 @@
       </c>
       <c r="D12" s="5"/>
     </row>
-    <row r="13" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="13" spans="1:4">
       <c r="A13" s="5" t="s">
-        <v>113</v>
+        <v>111</v>
       </c>
       <c r="B13" s="5">
         <v>50</v>
@@ -2808,9 +2790,9 @@
       </c>
       <c r="D13" s="5"/>
     </row>
-    <row r="14" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="14" spans="1:4">
       <c r="A14" s="5" t="s">
-        <v>114</v>
+        <v>112</v>
       </c>
       <c r="B14" s="5">
         <v>50</v>
@@ -2820,9 +2802,9 @@
       </c>
       <c r="D14" s="5"/>
     </row>
-    <row r="15" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="15" spans="1:4">
       <c r="A15" s="5" t="s">
-        <v>115</v>
+        <v>113</v>
       </c>
       <c r="B15" s="5">
         <v>50</v>
@@ -2832,9 +2814,9 @@
       </c>
       <c r="D15" s="5"/>
     </row>
-    <row r="16" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="16" spans="1:4">
       <c r="A16" s="5" t="s">
-        <v>116</v>
+        <v>114</v>
       </c>
       <c r="B16" s="5"/>
       <c r="C16" s="5">
@@ -2854,360 +2836,361 @@
 <file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{38B1429F-C7BD-4892-AF10-4DB5AFE45ACB}">
   <dimension ref="A5:C37"/>
-  <sheetFormatPr baseColWidth="10" defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
+  <sheetFormatPr baseColWidth="10" defaultRowHeight="13.7"/>
   <cols>
     <col min="1" max="1" width="27.77734375" customWidth="1"/>
     <col min="2" max="2" width="19.5546875" customWidth="1"/>
     <col min="3" max="3" width="37.6640625" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="5" spans="1:3" ht="21" x14ac:dyDescent="0.4">
-      <c r="A5" s="13" t="s">
+    <row r="5" spans="1:3" ht="20">
+      <c r="A5" s="30" t="s">
+        <v>71</v>
+      </c>
+      <c r="B5" s="31"/>
+      <c r="C5" s="31"/>
+    </row>
+    <row r="6" spans="1:3">
+      <c r="A6" t="s">
+        <v>72</v>
+      </c>
+    </row>
+    <row r="7" spans="1:3" ht="20">
+      <c r="A7" s="4"/>
+    </row>
+    <row r="8" spans="1:3">
+      <c r="A8" s="1" t="s">
+        <v>146</v>
+      </c>
+    </row>
+    <row r="9" spans="1:3">
+      <c r="A9" s="10" t="s">
         <v>73</v>
       </c>
-      <c r="B5" s="14"/>
-      <c r="C5" s="14"/>
-    </row>
-    <row r="6" spans="1:3" x14ac:dyDescent="0.3">
-      <c r="A6" t="s">
+      <c r="B9" s="10" t="s">
         <v>74</v>
       </c>
-    </row>
-    <row r="7" spans="1:3" ht="21" x14ac:dyDescent="0.4">
-      <c r="A7" s="4"/>
-    </row>
-    <row r="8" spans="1:3" x14ac:dyDescent="0.3">
-      <c r="A8" s="1" t="s">
-        <v>148</v>
-      </c>
-    </row>
-    <row r="9" spans="1:3" x14ac:dyDescent="0.3">
-      <c r="A9" s="10" t="s">
-        <v>75</v>
-      </c>
-      <c r="B9" s="10" t="s">
+      <c r="C9" s="10" t="s">
+        <v>105</v>
+      </c>
+    </row>
+    <row r="10" spans="1:3">
+      <c r="A10" t="s">
         <v>76</v>
       </c>
-      <c r="C9" s="10" t="s">
-        <v>107</v>
-      </c>
-    </row>
-    <row r="10" spans="1:3" x14ac:dyDescent="0.3">
-      <c r="A10" t="s">
+      <c r="B10" t="s">
+        <v>104</v>
+      </c>
+      <c r="C10" t="s">
+        <v>134</v>
+      </c>
+    </row>
+    <row r="11" spans="1:3">
+      <c r="A11" t="s">
+        <v>77</v>
+      </c>
+      <c r="B11" t="s">
+        <v>104</v>
+      </c>
+      <c r="C11" t="s">
+        <v>134</v>
+      </c>
+    </row>
+    <row r="12" spans="1:3">
+      <c r="A12" t="s">
         <v>78</v>
       </c>
-      <c r="B10" t="s">
-        <v>106</v>
-      </c>
-      <c r="C10" t="s">
-        <v>52</v>
-      </c>
-    </row>
-    <row r="11" spans="1:3" x14ac:dyDescent="0.3">
-      <c r="A11" t="s">
+      <c r="B12" t="s">
+        <v>104</v>
+      </c>
+      <c r="C12" t="s">
+        <v>134</v>
+      </c>
+    </row>
+    <row r="13" spans="1:3">
+      <c r="A13" t="s">
         <v>79</v>
       </c>
-      <c r="B11" t="s">
-        <v>106</v>
-      </c>
-      <c r="C11" t="s">
-        <v>52</v>
-      </c>
-    </row>
-    <row r="12" spans="1:3" x14ac:dyDescent="0.3">
-      <c r="A12" t="s">
+      <c r="B13" t="s">
+        <v>104</v>
+      </c>
+      <c r="C13" t="s">
+        <v>134</v>
+      </c>
+    </row>
+    <row r="14" spans="1:3">
+      <c r="A14" t="s">
         <v>80</v>
       </c>
-      <c r="B12" t="s">
-        <v>106</v>
-      </c>
-      <c r="C12" t="s">
-        <v>52</v>
-      </c>
-    </row>
-    <row r="13" spans="1:3" x14ac:dyDescent="0.3">
-      <c r="A13" t="s">
+      <c r="B14" t="s">
+        <v>104</v>
+      </c>
+      <c r="C14" t="s">
+        <v>134</v>
+      </c>
+    </row>
+    <row r="15" spans="1:3">
+      <c r="A15" t="s">
         <v>81</v>
       </c>
-      <c r="B13" t="s">
-        <v>106</v>
-      </c>
-      <c r="C13" t="s">
-        <v>52</v>
-      </c>
-    </row>
-    <row r="14" spans="1:3" x14ac:dyDescent="0.3">
-      <c r="A14" t="s">
+      <c r="B15" t="s">
+        <v>104</v>
+      </c>
+      <c r="C15" t="s">
+        <v>134</v>
+      </c>
+    </row>
+    <row r="16" spans="1:3">
+      <c r="A16" t="s">
         <v>82</v>
       </c>
-      <c r="B14" t="s">
-        <v>106</v>
-      </c>
-      <c r="C14" t="s">
-        <v>52</v>
-      </c>
-    </row>
-    <row r="15" spans="1:3" x14ac:dyDescent="0.3">
-      <c r="A15" t="s">
+      <c r="B16" t="s">
+        <v>104</v>
+      </c>
+      <c r="C16" t="s">
+        <v>134</v>
+      </c>
+    </row>
+    <row r="17" spans="1:3">
+      <c r="A17" t="s">
         <v>83</v>
       </c>
-      <c r="B15" t="s">
-        <v>106</v>
-      </c>
-      <c r="C15" t="s">
-        <v>52</v>
-      </c>
-    </row>
-    <row r="16" spans="1:3" x14ac:dyDescent="0.3">
-      <c r="A16" t="s">
+      <c r="B17" t="s">
+        <v>104</v>
+      </c>
+      <c r="C17" t="s">
+        <v>134</v>
+      </c>
+    </row>
+    <row r="18" spans="1:3">
+      <c r="A18" t="s">
         <v>84</v>
       </c>
-      <c r="B16" t="s">
-        <v>106</v>
-      </c>
-      <c r="C16" t="s">
-        <v>52</v>
-      </c>
-    </row>
-    <row r="17" spans="1:3" x14ac:dyDescent="0.3">
-      <c r="A17" t="s">
+      <c r="B18" t="s">
+        <v>104</v>
+      </c>
+      <c r="C18" t="s">
+        <v>134</v>
+      </c>
+    </row>
+    <row r="19" spans="1:3">
+      <c r="A19" t="s">
         <v>85</v>
       </c>
-      <c r="B17" t="s">
-        <v>106</v>
-      </c>
-      <c r="C17" t="s">
-        <v>52</v>
-      </c>
-    </row>
-    <row r="18" spans="1:3" x14ac:dyDescent="0.3">
-      <c r="A18" t="s">
+      <c r="B19" t="s">
+        <v>104</v>
+      </c>
+      <c r="C19" t="s">
+        <v>134</v>
+      </c>
+    </row>
+    <row r="20" spans="1:3">
+      <c r="A20" t="s">
         <v>86</v>
       </c>
-      <c r="B18" t="s">
-        <v>106</v>
-      </c>
-      <c r="C18" t="s">
-        <v>52</v>
-      </c>
-    </row>
-    <row r="19" spans="1:3" x14ac:dyDescent="0.3">
-      <c r="A19" t="s">
+      <c r="B20" t="s">
+        <v>104</v>
+      </c>
+      <c r="C20" t="s">
+        <v>134</v>
+      </c>
+    </row>
+    <row r="21" spans="1:3">
+      <c r="A21" t="s">
         <v>87</v>
       </c>
-      <c r="B19" t="s">
-        <v>106</v>
-      </c>
-      <c r="C19" t="s">
-        <v>52</v>
-      </c>
-    </row>
-    <row r="20" spans="1:3" x14ac:dyDescent="0.3">
-      <c r="A20" t="s">
+      <c r="B21" t="s">
+        <v>104</v>
+      </c>
+      <c r="C21" t="s">
+        <v>134</v>
+      </c>
+    </row>
+    <row r="22" spans="1:3">
+      <c r="A22" t="s">
         <v>88</v>
       </c>
-      <c r="B20" t="s">
-        <v>106</v>
-      </c>
-      <c r="C20" t="s">
-        <v>52</v>
-      </c>
-    </row>
-    <row r="21" spans="1:3" x14ac:dyDescent="0.3">
-      <c r="A21" t="s">
+      <c r="B22" t="s">
+        <v>104</v>
+      </c>
+      <c r="C22" t="s">
+        <v>134</v>
+      </c>
+    </row>
+    <row r="23" spans="1:3">
+      <c r="A23" t="s">
         <v>89</v>
       </c>
-      <c r="B21" t="s">
-        <v>106</v>
-      </c>
-      <c r="C21" t="s">
-        <v>52</v>
-      </c>
-    </row>
-    <row r="22" spans="1:3" x14ac:dyDescent="0.3">
-      <c r="A22" t="s">
+      <c r="B23" t="s">
+        <v>104</v>
+      </c>
+      <c r="C23" t="s">
+        <v>134</v>
+      </c>
+    </row>
+    <row r="24" spans="1:3">
+      <c r="A24" t="s">
         <v>90</v>
       </c>
-      <c r="B22" t="s">
-        <v>106</v>
-      </c>
-      <c r="C22" t="s">
-        <v>52</v>
-      </c>
-    </row>
-    <row r="23" spans="1:3" x14ac:dyDescent="0.3">
-      <c r="A23" t="s">
+      <c r="B24" t="s">
+        <v>104</v>
+      </c>
+      <c r="C24" t="s">
+        <v>134</v>
+      </c>
+    </row>
+    <row r="25" spans="1:3">
+      <c r="A25" t="s">
         <v>91</v>
       </c>
-      <c r="B23" t="s">
-        <v>106</v>
-      </c>
-      <c r="C23" t="s">
-        <v>52</v>
-      </c>
-    </row>
-    <row r="24" spans="1:3" x14ac:dyDescent="0.3">
-      <c r="A24" t="s">
+      <c r="B25" t="s">
+        <v>104</v>
+      </c>
+      <c r="C25" t="s">
+        <v>134</v>
+      </c>
+    </row>
+    <row r="26" spans="1:3">
+      <c r="A26" t="s">
         <v>92</v>
       </c>
-      <c r="B24" t="s">
-        <v>106</v>
-      </c>
-      <c r="C24" t="s">
-        <v>52</v>
-      </c>
-    </row>
-    <row r="25" spans="1:3" x14ac:dyDescent="0.3">
-      <c r="A25" t="s">
+      <c r="B26" t="s">
+        <v>104</v>
+      </c>
+      <c r="C26" t="s">
+        <v>134</v>
+      </c>
+    </row>
+    <row r="27" spans="1:3">
+      <c r="A27" t="s">
         <v>93</v>
       </c>
-      <c r="B25" t="s">
-        <v>106</v>
-      </c>
-      <c r="C25" t="s">
-        <v>52</v>
-      </c>
-    </row>
-    <row r="26" spans="1:3" x14ac:dyDescent="0.3">
-      <c r="A26" t="s">
+      <c r="B27" t="s">
+        <v>104</v>
+      </c>
+      <c r="C27" t="s">
+        <v>134</v>
+      </c>
+    </row>
+    <row r="28" spans="1:3">
+      <c r="A28" t="s">
         <v>94</v>
       </c>
-      <c r="B26" t="s">
-        <v>106</v>
-      </c>
-      <c r="C26" t="s">
-        <v>52</v>
-      </c>
-    </row>
-    <row r="27" spans="1:3" x14ac:dyDescent="0.3">
-      <c r="A27" t="s">
+      <c r="B28" t="s">
+        <v>104</v>
+      </c>
+      <c r="C28" t="s">
+        <v>134</v>
+      </c>
+    </row>
+    <row r="29" spans="1:3">
+      <c r="A29" t="s">
         <v>95</v>
       </c>
-      <c r="B27" t="s">
-        <v>106</v>
-      </c>
-      <c r="C27" t="s">
-        <v>52</v>
-      </c>
-    </row>
-    <row r="28" spans="1:3" x14ac:dyDescent="0.3">
-      <c r="A28" t="s">
+      <c r="B29" t="s">
+        <v>104</v>
+      </c>
+      <c r="C29" t="s">
+        <v>134</v>
+      </c>
+    </row>
+    <row r="30" spans="1:3">
+      <c r="A30" t="s">
         <v>96</v>
       </c>
-      <c r="B28" t="s">
-        <v>106</v>
-      </c>
-      <c r="C28" t="s">
-        <v>52</v>
-      </c>
-    </row>
-    <row r="29" spans="1:3" x14ac:dyDescent="0.3">
-      <c r="A29" t="s">
+      <c r="B30" t="s">
+        <v>104</v>
+      </c>
+      <c r="C30" t="s">
+        <v>134</v>
+      </c>
+    </row>
+    <row r="31" spans="1:3">
+      <c r="A31" t="s">
         <v>97</v>
       </c>
-      <c r="B29" t="s">
-        <v>106</v>
-      </c>
-      <c r="C29" t="s">
-        <v>52</v>
-      </c>
-    </row>
-    <row r="30" spans="1:3" x14ac:dyDescent="0.3">
-      <c r="A30" t="s">
+      <c r="B31" t="s">
+        <v>104</v>
+      </c>
+      <c r="C31" t="s">
+        <v>134</v>
+      </c>
+    </row>
+    <row r="32" spans="1:3">
+      <c r="A32" t="s">
         <v>98</v>
       </c>
-      <c r="B30" t="s">
-        <v>106</v>
-      </c>
-      <c r="C30" t="s">
-        <v>52</v>
-      </c>
-    </row>
-    <row r="31" spans="1:3" x14ac:dyDescent="0.3">
-      <c r="A31" t="s">
+      <c r="B32" t="s">
+        <v>104</v>
+      </c>
+      <c r="C32" t="s">
+        <v>134</v>
+      </c>
+    </row>
+    <row r="33" spans="1:3">
+      <c r="A33" t="s">
         <v>99</v>
       </c>
-      <c r="B31" t="s">
-        <v>106</v>
-      </c>
-      <c r="C31" t="s">
-        <v>52</v>
-      </c>
-    </row>
-    <row r="32" spans="1:3" x14ac:dyDescent="0.3">
-      <c r="A32" t="s">
+      <c r="B33" t="s">
+        <v>104</v>
+      </c>
+      <c r="C33" t="s">
+        <v>134</v>
+      </c>
+    </row>
+    <row r="34" spans="1:3">
+      <c r="A34" t="s">
         <v>100</v>
       </c>
-      <c r="B32" t="s">
-        <v>106</v>
-      </c>
-      <c r="C32" t="s">
-        <v>52</v>
-      </c>
-    </row>
-    <row r="33" spans="1:3" x14ac:dyDescent="0.3">
-      <c r="A33" t="s">
+      <c r="B34" t="s">
+        <v>104</v>
+      </c>
+      <c r="C34" t="s">
+        <v>134</v>
+      </c>
+    </row>
+    <row r="35" spans="1:3">
+      <c r="A35" t="s">
         <v>101</v>
       </c>
-      <c r="B33" t="s">
-        <v>106</v>
-      </c>
-      <c r="C33" t="s">
-        <v>52</v>
-      </c>
-    </row>
-    <row r="34" spans="1:3" x14ac:dyDescent="0.3">
-      <c r="A34" t="s">
+      <c r="B35" t="s">
+        <v>104</v>
+      </c>
+      <c r="C35" t="s">
+        <v>134</v>
+      </c>
+    </row>
+    <row r="36" spans="1:3">
+      <c r="A36" t="s">
         <v>102</v>
       </c>
-      <c r="B34" t="s">
-        <v>106</v>
-      </c>
-      <c r="C34" t="s">
-        <v>52</v>
-      </c>
-    </row>
-    <row r="35" spans="1:3" x14ac:dyDescent="0.3">
-      <c r="A35" t="s">
+      <c r="B36" t="s">
+        <v>104</v>
+      </c>
+      <c r="C36" t="s">
+        <v>134</v>
+      </c>
+    </row>
+    <row r="37" spans="1:3">
+      <c r="A37" t="s">
         <v>103</v>
       </c>
-      <c r="B35" t="s">
-        <v>106</v>
-      </c>
-      <c r="C35" t="s">
-        <v>52</v>
-      </c>
-    </row>
-    <row r="36" spans="1:3" x14ac:dyDescent="0.3">
-      <c r="A36" t="s">
+      <c r="B37" t="s">
         <v>104</v>
       </c>
-      <c r="B36" t="s">
-        <v>106</v>
-      </c>
-      <c r="C36" t="s">
-        <v>52</v>
-      </c>
-    </row>
-    <row r="37" spans="1:3" x14ac:dyDescent="0.3">
-      <c r="A37" t="s">
-        <v>105</v>
-      </c>
-      <c r="B37" t="s">
-        <v>106</v>
-      </c>
       <c r="C37" t="s">
-        <v>52</v>
+        <v>134</v>
       </c>
     </row>
   </sheetData>
   <mergeCells count="1">
     <mergeCell ref="A5:C5"/>
   </mergeCells>
+  <phoneticPr fontId="5" type="noConversion"/>
   <pageMargins left="0.7" right="0.7" top="0.78740157499999996" bottom="0.78740157499999996" header="0.3" footer="0.3"/>
   <extLst>
     <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{CCE6A557-97BC-4b89-ADB6-D9C93CAAB3DF}">
-      <x14:dataValidations xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main" count="2">
+      <x14:dataValidations xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main" count="3">
         <x14:dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" xr:uid="{64C27FEB-0949-4523-8ACE-6A67A7590785}">
           <x14:formula1>
             <xm:f>Hidden_Lists!$F$2:$F$30</xm:f>
@@ -3218,7 +3201,13 @@
           <x14:formula1>
             <xm:f>Basics!$F$10:$F$202</xm:f>
           </x14:formula1>
-          <xm:sqref>C10:C1107</xm:sqref>
+          <xm:sqref>C166:C1107</xm:sqref>
+        </x14:dataValidation>
+        <x14:dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" xr:uid="{12DB46A2-6060-4A34-85F0-762BFF0F1C9A}">
+          <x14:formula1>
+            <xm:f>Basics!$F$10:$F$100</xm:f>
+          </x14:formula1>
+          <xm:sqref>C10:C165</xm:sqref>
         </x14:dataValidation>
       </x14:dataValidations>
     </ext>
@@ -3232,56 +3221,56 @@
     <tabColor rgb="FF92D050"/>
   </sheetPr>
   <dimension ref="A5:O60"/>
-  <sheetFormatPr baseColWidth="10" defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
+  <sheetFormatPr baseColWidth="10" defaultRowHeight="13.7"/>
   <cols>
     <col min="1" max="1" width="25.44140625" customWidth="1"/>
     <col min="2" max="2" width="31.21875" customWidth="1"/>
-    <col min="3" max="3" width="42.44140625" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="46.27734375" customWidth="1"/>
     <col min="4" max="4" width="23.6640625" bestFit="1" customWidth="1"/>
     <col min="5" max="5" width="21.6640625" style="8" bestFit="1" customWidth="1"/>
     <col min="6" max="6" width="19.88671875" bestFit="1" customWidth="1"/>
-    <col min="7" max="7" width="25.21875" bestFit="1" customWidth="1"/>
+    <col min="7" max="7" width="31.71875" customWidth="1"/>
     <col min="8" max="8" width="23.109375" bestFit="1" customWidth="1"/>
     <col min="9" max="9" width="21.6640625" bestFit="1" customWidth="1"/>
     <col min="10" max="10" width="23.5546875" bestFit="1" customWidth="1"/>
     <col min="11" max="11" width="29.77734375" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="5" spans="1:15" ht="21" x14ac:dyDescent="0.4">
-      <c r="A5" s="18" t="s">
-        <v>166</v>
-      </c>
-      <c r="B5" s="19"/>
-      <c r="C5" s="19"/>
-      <c r="D5" s="18"/>
-      <c r="E5" s="19"/>
-      <c r="F5" s="19"/>
-      <c r="G5" s="19"/>
-      <c r="H5" s="19"/>
-      <c r="I5" s="18"/>
-      <c r="J5" s="19"/>
-    </row>
-    <row r="7" spans="1:15" x14ac:dyDescent="0.3">
+    <row r="5" spans="1:15" ht="20">
+      <c r="A5" s="16" t="s">
+        <v>164</v>
+      </c>
+      <c r="B5" s="17"/>
+      <c r="C5" s="17"/>
+      <c r="D5" s="16"/>
+      <c r="E5" s="17"/>
+      <c r="F5" s="17"/>
+      <c r="G5" s="17"/>
+      <c r="H5" s="17"/>
+      <c r="I5" s="16"/>
+      <c r="J5" s="17"/>
+    </row>
+    <row r="7" spans="1:15">
       <c r="A7" t="s">
-        <v>162</v>
-      </c>
-    </row>
-    <row r="8" spans="1:15" x14ac:dyDescent="0.3">
-      <c r="A8" s="30" t="s">
-        <v>146</v>
-      </c>
-    </row>
-    <row r="9" spans="1:15" s="3" customFormat="1" ht="18" x14ac:dyDescent="0.35">
-      <c r="A9" s="26" t="s">
-        <v>147</v>
-      </c>
-      <c r="B9" s="26"/>
-    </row>
-    <row r="11" spans="1:15" ht="15.6" x14ac:dyDescent="0.3">
-      <c r="A11" s="23" t="s">
+        <v>160</v>
+      </c>
+    </row>
+    <row r="8" spans="1:15">
+      <c r="A8" s="27" t="s">
+        <v>144</v>
+      </c>
+    </row>
+    <row r="9" spans="1:15" s="3" customFormat="1" ht="17.7">
+      <c r="A9" s="23" t="s">
         <v>145</v>
       </c>
-      <c r="B11" s="24" t="str">
+      <c r="B9" s="23"/>
+    </row>
+    <row r="11" spans="1:15" ht="15.35">
+      <c r="A11" s="20" t="s">
+        <v>143</v>
+      </c>
+      <c r="B11" s="21" t="str">
         <f>Basics!H1 &amp; " AddOn " &amp; Basics!H2</f>
         <v>MassPrep® AddOn TDM Series A</v>
       </c>
@@ -3290,19 +3279,19 @@
       <c r="N11" s="2"/>
       <c r="O11" s="2"/>
     </row>
-    <row r="12" spans="1:15" ht="15.6" x14ac:dyDescent="0.3">
-      <c r="A12" s="23" t="s">
-        <v>139</v>
-      </c>
-      <c r="B12" s="25">
+    <row r="12" spans="1:15" ht="15.35">
+      <c r="A12" s="20" t="s">
+        <v>137</v>
+      </c>
+      <c r="B12" s="22">
         <f>Basics!H3</f>
         <v>42952</v>
       </c>
     </row>
-    <row r="13" spans="1:15" ht="15.6" x14ac:dyDescent="0.3">
+    <row r="13" spans="1:15" ht="15.35">
       <c r="A13" s="2"/>
     </row>
-    <row r="15" spans="1:15" x14ac:dyDescent="0.3">
+    <row r="15" spans="1:15">
       <c r="F15" t="str">
         <f>IF(E15&lt;&gt;"",_xlfn.XLOOKUP(E15, Basics!F13:F93, Basics!D13:D93) &amp; "-A","")</f>
         <v/>
@@ -3312,45 +3301,45 @@
         <v/>
       </c>
     </row>
-    <row r="16" spans="1:15" ht="18" x14ac:dyDescent="0.35">
-      <c r="A16" s="27" t="s">
-        <v>168</v>
-      </c>
-      <c r="B16" s="26"/>
-      <c r="C16" s="26"/>
-      <c r="D16" s="26"/>
-      <c r="E16" s="26"/>
-      <c r="F16" s="26"/>
-      <c r="G16" s="26"/>
-    </row>
-    <row r="17" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="16" spans="1:15" ht="17.7">
+      <c r="A16" s="24" t="s">
+        <v>166</v>
+      </c>
+      <c r="B16" s="23"/>
+      <c r="C16" s="23"/>
+      <c r="D16" s="23"/>
+      <c r="E16" s="23"/>
+      <c r="F16" s="23"/>
+      <c r="G16" s="23"/>
+    </row>
+    <row r="17" spans="1:7">
       <c r="A17" s="8"/>
       <c r="E17"/>
     </row>
-    <row r="18" spans="1:7" ht="15.6" x14ac:dyDescent="0.3">
+    <row r="18" spans="1:7" ht="15.35">
       <c r="A18" s="2" t="s">
-        <v>167</v>
+        <v>165</v>
       </c>
       <c r="B18" s="2" t="s">
-        <v>151</v>
+        <v>149</v>
       </c>
       <c r="C18" s="2" t="s">
-        <v>165</v>
+        <v>163</v>
       </c>
       <c r="D18" s="2" t="s">
-        <v>161</v>
+        <v>159</v>
       </c>
       <c r="E18" s="2" t="s">
-        <v>149</v>
+        <v>147</v>
       </c>
       <c r="F18" s="2" t="s">
+        <v>148</v>
+      </c>
+      <c r="G18" s="2" t="s">
         <v>150</v>
       </c>
-      <c r="G18" s="2" t="s">
-        <v>152</v>
-      </c>
-    </row>
-    <row r="19" spans="1:7" x14ac:dyDescent="0.3">
+    </row>
+    <row r="19" spans="1:7">
       <c r="A19" s="8" t="str" cm="1">
         <f t="array" ref="A19:A21">IFERROR(_xlfn._xlws.SORT(_xlfn.UNIQUE(_xlfn._xlws.FILTER(Basics!F10:F90,(Basics!F10:F90&lt;&gt;"Basic Kit")*(Basics!F10:F90&lt;&gt;"")))),"No Assays found!")</f>
         <v>Antidepressants 1/EXTENDED</v>
@@ -3380,7 +3369,7 @@
         <v>Antidepressants 1/EXTENDED</v>
       </c>
     </row>
-    <row r="20" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="20" spans="1:7">
       <c r="A20" s="8" t="str">
         <v>Antiepileptic Drugs XT2</v>
       </c>
@@ -3409,7 +3398,7 @@
         <v>Antiepileptic Drugs XT2</v>
       </c>
     </row>
-    <row r="21" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="21" spans="1:7">
       <c r="A21" s="8" t="str">
         <v>Neuroleptics 2/EXTENDED 2</v>
       </c>
@@ -3438,7 +3427,7 @@
         <v>Neuroleptics 2/EXTENDED 2</v>
       </c>
     </row>
-    <row r="22" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="22" spans="1:7">
       <c r="A22" s="8"/>
       <c r="B22" t="str">
         <f>IF(A22&lt;&gt;"",_xlfn.XLOOKUP(A22, Basics!F13:F93, Basics!D13:D93) &amp; "-A","")</f>
@@ -3465,7 +3454,7 @@
         <v/>
       </c>
     </row>
-    <row r="23" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="23" spans="1:7">
       <c r="A23" s="8"/>
       <c r="B23" t="str">
         <f>IF(A23&lt;&gt;"",_xlfn.XLOOKUP(A23, Basics!F14:F94, Basics!D14:D94) &amp; "-A","")</f>
@@ -3492,7 +3481,7 @@
         <v/>
       </c>
     </row>
-    <row r="24" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="24" spans="1:7">
       <c r="A24" s="8"/>
       <c r="B24" t="str">
         <f>IF(A24&lt;&gt;"",_xlfn.XLOOKUP(A24, Basics!F15:F95, Basics!D15:D95) &amp; "-A","")</f>
@@ -3519,7 +3508,7 @@
         <v/>
       </c>
     </row>
-    <row r="25" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="25" spans="1:7">
       <c r="A25" s="8"/>
       <c r="B25" t="str">
         <f>IF(A25&lt;&gt;"",_xlfn.XLOOKUP(A25, Basics!F16:F96, Basics!D16:D96) &amp; "-A","")</f>
@@ -3546,7 +3535,7 @@
         <v/>
       </c>
     </row>
-    <row r="26" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="26" spans="1:7">
       <c r="A26" s="8"/>
       <c r="B26" t="str">
         <f>IF(A26&lt;&gt;"",_xlfn.XLOOKUP(A26, Basics!F17:F97, Basics!D17:D97) &amp; "-A","")</f>
@@ -3573,7 +3562,7 @@
         <v/>
       </c>
     </row>
-    <row r="27" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="27" spans="1:7">
       <c r="A27" s="8"/>
       <c r="B27" t="str">
         <f>IF(A27&lt;&gt;"",_xlfn.XLOOKUP(A27, Basics!F18:F98, Basics!D18:D98) &amp; "-A","")</f>
@@ -3600,7 +3589,7 @@
         <v/>
       </c>
     </row>
-    <row r="28" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="28" spans="1:7">
       <c r="A28" s="8"/>
       <c r="B28" t="str">
         <f>IF(A28&lt;&gt;"",_xlfn.XLOOKUP(A28, Basics!F19:F99, Basics!D19:D99) &amp; "-A","")</f>
@@ -3627,7 +3616,7 @@
         <v/>
       </c>
     </row>
-    <row r="29" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="29" spans="1:7">
       <c r="A29" s="8"/>
       <c r="B29" t="str">
         <f>IF(A29&lt;&gt;"",_xlfn.XLOOKUP(A29, Basics!F20:F100, Basics!D20:D100) &amp; "-A","")</f>
@@ -3654,7 +3643,7 @@
         <v/>
       </c>
     </row>
-    <row r="30" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="30" spans="1:7">
       <c r="A30" s="8"/>
       <c r="B30" t="str">
         <f>IF(A30&lt;&gt;"",_xlfn.XLOOKUP(A30, Basics!F21:F101, Basics!D21:D101) &amp; "-A","")</f>
@@ -3681,7 +3670,7 @@
         <v/>
       </c>
     </row>
-    <row r="31" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="31" spans="1:7">
       <c r="A31" s="8"/>
       <c r="B31" t="str">
         <f>IF(A31&lt;&gt;"",_xlfn.XLOOKUP(A31, Basics!F22:F102, Basics!D22:D102) &amp; "-A","")</f>
@@ -3708,7 +3697,7 @@
         <v/>
       </c>
     </row>
-    <row r="32" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="32" spans="1:7">
       <c r="A32" s="8"/>
       <c r="B32" t="str">
         <f>IF(A32&lt;&gt;"",_xlfn.XLOOKUP(A32, Basics!F23:F103, Basics!D23:D103) &amp; "-A","")</f>
@@ -3735,7 +3724,7 @@
         <v/>
       </c>
     </row>
-    <row r="33" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="33" spans="1:7">
       <c r="A33" s="8"/>
       <c r="B33" t="str">
         <f>IF(A33&lt;&gt;"",_xlfn.XLOOKUP(A33, Basics!F24:F104, Basics!D24:D104) &amp; "-A","")</f>
@@ -3762,7 +3751,7 @@
         <v/>
       </c>
     </row>
-    <row r="34" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="34" spans="1:7">
       <c r="A34" s="8"/>
       <c r="B34" t="str">
         <f>IF(A34&lt;&gt;"",_xlfn.XLOOKUP(A34, Basics!F25:F105, Basics!D25:D105) &amp; "-A","")</f>
@@ -3789,7 +3778,7 @@
         <v/>
       </c>
     </row>
-    <row r="35" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="35" spans="1:7">
       <c r="A35" s="8"/>
       <c r="B35" t="str">
         <f>IF(A35&lt;&gt;"",_xlfn.XLOOKUP(A35, Basics!F26:F106, Basics!D26:D106) &amp; "-A","")</f>
@@ -3816,7 +3805,7 @@
         <v/>
       </c>
     </row>
-    <row r="36" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="36" spans="1:7">
       <c r="A36" s="8"/>
       <c r="B36" t="str">
         <f>IF(A36&lt;&gt;"",_xlfn.XLOOKUP(A36, Basics!F27:F107, Basics!D27:D107) &amp; "-A","")</f>
@@ -3843,7 +3832,7 @@
         <v/>
       </c>
     </row>
-    <row r="37" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="37" spans="1:7">
       <c r="A37" s="8"/>
       <c r="B37" t="str">
         <f>IF(A37&lt;&gt;"",_xlfn.XLOOKUP(A37, Basics!F28:F108, Basics!D28:D108) &amp; "-A","")</f>
@@ -3870,7 +3859,7 @@
         <v/>
       </c>
     </row>
-    <row r="38" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="38" spans="1:7">
       <c r="A38" s="8"/>
       <c r="B38" t="str">
         <f>IF(A38&lt;&gt;"",_xlfn.XLOOKUP(A38, Basics!F29:F109, Basics!D29:D109) &amp; "-A","")</f>
@@ -3897,7 +3886,7 @@
         <v/>
       </c>
     </row>
-    <row r="39" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="39" spans="1:7">
       <c r="A39" s="8"/>
       <c r="B39" t="str">
         <f>IF(A39&lt;&gt;"",_xlfn.XLOOKUP(A39, Basics!F30:F110, Basics!D30:D110) &amp; "-A","")</f>
@@ -3924,7 +3913,7 @@
         <v/>
       </c>
     </row>
-    <row r="40" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="40" spans="1:7">
       <c r="A40" s="8"/>
       <c r="B40" t="str">
         <f>IF(A40&lt;&gt;"",_xlfn.XLOOKUP(A40, Basics!F31:F111, Basics!D31:D111) &amp; "-A","")</f>
@@ -3951,7 +3940,7 @@
         <v/>
       </c>
     </row>
-    <row r="41" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="41" spans="1:7">
       <c r="A41" s="8"/>
       <c r="B41" t="str">
         <f>IF(A41&lt;&gt;"",_xlfn.XLOOKUP(A41, Basics!F32:F112, Basics!D32:D112) &amp; "-A","")</f>
@@ -3978,7 +3967,7 @@
         <v/>
       </c>
     </row>
-    <row r="42" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="42" spans="1:7">
       <c r="A42" s="8"/>
       <c r="B42" t="str">
         <f>IF(A42&lt;&gt;"",_xlfn.XLOOKUP(A42, Basics!F33:F113, Basics!D33:D113) &amp; "-A","")</f>
@@ -4005,7 +3994,7 @@
         <v/>
       </c>
     </row>
-    <row r="43" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="43" spans="1:7">
       <c r="A43" s="8"/>
       <c r="B43" t="str">
         <f>IF(A43&lt;&gt;"",_xlfn.XLOOKUP(A43, Basics!F34:F114, Basics!D34:D114) &amp; "-A","")</f>
@@ -4032,7 +4021,7 @@
         <v/>
       </c>
     </row>
-    <row r="44" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="44" spans="1:7">
       <c r="A44" s="8"/>
       <c r="B44" t="str">
         <f>IF(A44&lt;&gt;"",_xlfn.XLOOKUP(A44, Basics!F35:F115, Basics!D35:D115) &amp; "-A","")</f>
@@ -4059,7 +4048,7 @@
         <v/>
       </c>
     </row>
-    <row r="45" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="45" spans="1:7">
       <c r="A45" s="8"/>
       <c r="B45" t="str">
         <f>IF(A45&lt;&gt;"",_xlfn.XLOOKUP(A45, Basics!F36:F116, Basics!D36:D116) &amp; "-A","")</f>
@@ -4086,7 +4075,7 @@
         <v/>
       </c>
     </row>
-    <row r="46" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="46" spans="1:7">
       <c r="A46" s="8"/>
       <c r="B46" t="str">
         <f>IF(A46&lt;&gt;"",_xlfn.XLOOKUP(A46, Basics!F37:F117, Basics!D37:D117) &amp; "-A","")</f>
@@ -4113,7 +4102,7 @@
         <v/>
       </c>
     </row>
-    <row r="47" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="47" spans="1:7">
       <c r="A47" s="8"/>
       <c r="B47" t="str">
         <f>IF(A47&lt;&gt;"",_xlfn.XLOOKUP(A47, Basics!F38:F118, Basics!D38:D118) &amp; "-A","")</f>
@@ -4140,7 +4129,7 @@
         <v/>
       </c>
     </row>
-    <row r="48" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="48" spans="1:7">
       <c r="A48" s="8"/>
       <c r="B48" t="str">
         <f>IF(A48&lt;&gt;"",_xlfn.XLOOKUP(A48, Basics!F39:F119, Basics!D39:D119) &amp; "-A","")</f>
@@ -4167,7 +4156,7 @@
         <v/>
       </c>
     </row>
-    <row r="49" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="49" spans="1:7">
       <c r="A49" s="8"/>
       <c r="B49" t="str">
         <f>IF(A49&lt;&gt;"",_xlfn.XLOOKUP(A49, Basics!F40:F120, Basics!D40:D120) &amp; "-A","")</f>
@@ -4194,7 +4183,7 @@
         <v/>
       </c>
     </row>
-    <row r="50" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="50" spans="1:7">
       <c r="A50" s="8"/>
       <c r="B50" t="str">
         <f>IF(A50&lt;&gt;"",_xlfn.XLOOKUP(A50, Basics!F41:F121, Basics!D41:D121) &amp; "-A","")</f>
@@ -4221,7 +4210,7 @@
         <v/>
       </c>
     </row>
-    <row r="51" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="51" spans="1:7">
       <c r="A51" s="8"/>
       <c r="B51" t="str">
         <f>IF(A51&lt;&gt;"",_xlfn.XLOOKUP(A51, Basics!F42:F122, Basics!D42:D122) &amp; "-A","")</f>
@@ -4248,7 +4237,7 @@
         <v/>
       </c>
     </row>
-    <row r="52" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="52" spans="1:7">
       <c r="A52" s="8"/>
       <c r="B52" t="str">
         <f>IF(A52&lt;&gt;"",_xlfn.XLOOKUP(A52, Basics!F43:F123, Basics!D43:D123) &amp; "-A","")</f>
@@ -4275,7 +4264,7 @@
         <v/>
       </c>
     </row>
-    <row r="53" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="53" spans="1:7">
       <c r="A53" s="8"/>
       <c r="B53" t="str">
         <f>IF(A53&lt;&gt;"",_xlfn.XLOOKUP(A53, Basics!F44:F124, Basics!D44:D124) &amp; "-A","")</f>
@@ -4302,7 +4291,7 @@
         <v/>
       </c>
     </row>
-    <row r="54" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="54" spans="1:7">
       <c r="A54" s="8"/>
       <c r="B54" t="str">
         <f>IF(A54&lt;&gt;"",_xlfn.XLOOKUP(A54, Basics!F45:F125, Basics!D45:D125) &amp; "-A","")</f>
@@ -4329,7 +4318,7 @@
         <v/>
       </c>
     </row>
-    <row r="55" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="55" spans="1:7">
       <c r="A55" s="8"/>
       <c r="B55" t="str">
         <f>IF(A55&lt;&gt;"",_xlfn.XLOOKUP(A55, Basics!F46:F126, Basics!D46:D126) &amp; "-A","")</f>
@@ -4356,7 +4345,7 @@
         <v/>
       </c>
     </row>
-    <row r="56" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="56" spans="1:7">
       <c r="A56" s="8"/>
       <c r="B56" t="str">
         <f>IF(A56&lt;&gt;"",_xlfn.XLOOKUP(A56, Basics!F47:F127, Basics!D47:D127) &amp; "-A","")</f>
@@ -4383,7 +4372,7 @@
         <v/>
       </c>
     </row>
-    <row r="57" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="57" spans="1:7">
       <c r="A57" s="8"/>
       <c r="B57" t="str">
         <f>IF(A57&lt;&gt;"",_xlfn.XLOOKUP(A57, Basics!F48:F128, Basics!D48:D128) &amp; "-A","")</f>
@@ -4410,7 +4399,7 @@
         <v/>
       </c>
     </row>
-    <row r="58" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="58" spans="1:7">
       <c r="A58" s="8"/>
       <c r="B58" t="str">
         <f>IF(A58&lt;&gt;"",_xlfn.XLOOKUP(A58, Basics!F49:F129, Basics!D49:D129) &amp; "-A","")</f>
@@ -4437,7 +4426,7 @@
         <v/>
       </c>
     </row>
-    <row r="59" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="59" spans="1:7">
       <c r="A59" s="8"/>
       <c r="B59" t="str">
         <f>IF(A59&lt;&gt;"",_xlfn.XLOOKUP(A59, Basics!F50:F130, Basics!D50:D130) &amp; "-A","")</f>
@@ -4464,7 +4453,7 @@
         <v/>
       </c>
     </row>
-    <row r="60" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="60" spans="1:7">
       <c r="A60" s="8"/>
       <c r="B60" t="str">
         <f>IF(A60&lt;&gt;"",_xlfn.XLOOKUP(A60, Basics!F51:F131, Basics!D51:D131) &amp; "-A","")</f>
@@ -4492,15 +4481,14 @@
       </c>
     </row>
   </sheetData>
-  <sheetProtection algorithmName="SHA-512" hashValue="WLSjFigJXYz2zm2X4TC6xs891KUEot6M/pC8IF7li8fCltH278t03WMMlUo7D1R3uh1fIFzPv4y2xqVBri5Kcg==" saltValue="0z++ceF9MpHz/5bCYsR4nA==" spinCount="100000" sheet="1" objects="1" scenarios="1"/>
   <pageMargins left="0.7" right="0.7" top="0.78740157499999996" bottom="0.78740157499999996" header="0.3" footer="0.3"/>
 </worksheet>
 </file>
 
 <file path=xl/worksheets/sheet6.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{B2C21798-10B0-4CA7-B3A5-83D00D987A71}">
-  <dimension ref="A1:G13"/>
-  <sheetFormatPr baseColWidth="10" defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
+  <dimension ref="A1:I13"/>
+  <sheetFormatPr baseColWidth="10" defaultRowHeight="13.7"/>
   <cols>
     <col min="1" max="1" width="27.33203125" bestFit="1" customWidth="1"/>
     <col min="3" max="3" width="18.88671875" bestFit="1" customWidth="1"/>
@@ -4510,7 +4498,7 @@
     <col min="7" max="7" width="24.6640625" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:7" s="1" customFormat="1" x14ac:dyDescent="0.3">
+    <row r="1" spans="1:9" s="1" customFormat="1">
       <c r="A1" s="1" t="s">
         <v>3</v>
       </c>
@@ -4527,13 +4515,13 @@
         <v>32</v>
       </c>
       <c r="F1" s="1" t="s">
-        <v>76</v>
+        <v>74</v>
       </c>
       <c r="G1" s="1" t="s">
-        <v>125</v>
-      </c>
-    </row>
-    <row r="2" spans="1:7" x14ac:dyDescent="0.3">
+        <v>123</v>
+      </c>
+    </row>
+    <row r="2" spans="1:9">
       <c r="A2" t="s">
         <v>7</v>
       </c>
@@ -4544,19 +4532,22 @@
         <v>16</v>
       </c>
       <c r="D2" t="s">
-        <v>133</v>
+        <v>131</v>
       </c>
       <c r="E2" t="s">
         <v>12</v>
       </c>
       <c r="F2" t="s">
-        <v>77</v>
+        <v>75</v>
       </c>
       <c r="G2">
         <v>10</v>
       </c>
-    </row>
-    <row r="3" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="I2" t="s">
+        <v>167</v>
+      </c>
+    </row>
+    <row r="3" spans="1:9">
       <c r="A3" t="s">
         <v>8</v>
       </c>
@@ -4567,16 +4558,19 @@
         <v>17</v>
       </c>
       <c r="D3" t="s">
-        <v>134</v>
+        <v>132</v>
       </c>
       <c r="E3" t="s">
         <v>33</v>
       </c>
       <c r="F3" t="s">
-        <v>106</v>
-      </c>
-    </row>
-    <row r="4" spans="1:7" x14ac:dyDescent="0.3">
+        <v>104</v>
+      </c>
+      <c r="I3" t="s">
+        <v>168</v>
+      </c>
+    </row>
+    <row r="4" spans="1:9">
       <c r="A4" t="s">
         <v>9</v>
       </c>
@@ -4592,8 +4586,9 @@
       <c r="E4" t="s">
         <v>34</v>
       </c>
-    </row>
-    <row r="5" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="I4" s="29"/>
+    </row>
+    <row r="5" spans="1:9" ht="177.7">
       <c r="A5" t="s">
         <v>11</v>
       </c>
@@ -4609,8 +4604,11 @@
       <c r="E5" t="s">
         <v>35</v>
       </c>
-    </row>
-    <row r="6" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="I5" s="29" t="s">
+        <v>169</v>
+      </c>
+    </row>
+    <row r="6" spans="1:9">
       <c r="A6" t="s">
         <v>10</v>
       </c>
@@ -4621,10 +4619,10 @@
         <v>29</v>
       </c>
       <c r="E6" t="s">
-        <v>121</v>
-      </c>
-    </row>
-    <row r="7" spans="1:7" x14ac:dyDescent="0.3">
+        <v>119</v>
+      </c>
+    </row>
+    <row r="7" spans="1:9">
       <c r="A7" t="s">
         <v>43</v>
       </c>
@@ -4635,9 +4633,9 @@
         <v>30</v>
       </c>
     </row>
-    <row r="8" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="8" spans="1:9">
       <c r="A8" t="s">
-        <v>131</v>
+        <v>129</v>
       </c>
       <c r="C8" t="s">
         <v>46</v>
@@ -4646,35 +4644,35 @@
         <v>31</v>
       </c>
     </row>
-    <row r="9" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="9" spans="1:9">
       <c r="A9" t="s">
         <v>44</v>
       </c>
       <c r="C9" t="s">
-        <v>67</v>
-      </c>
-    </row>
-    <row r="10" spans="1:7" x14ac:dyDescent="0.3">
+        <v>65</v>
+      </c>
+    </row>
+    <row r="10" spans="1:9">
       <c r="A10" t="s">
-        <v>142</v>
+        <v>140</v>
       </c>
       <c r="C10" t="s">
-        <v>68</v>
-      </c>
-    </row>
-    <row r="11" spans="1:7" x14ac:dyDescent="0.3">
+        <v>66</v>
+      </c>
+    </row>
+    <row r="11" spans="1:9">
       <c r="A11" t="s">
-        <v>143</v>
-      </c>
-    </row>
-    <row r="12" spans="1:7" x14ac:dyDescent="0.3">
+        <v>141</v>
+      </c>
+    </row>
+    <row r="12" spans="1:9">
       <c r="A12" t="s">
         <v>45</v>
       </c>
     </row>
-    <row r="13" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="13" spans="1:9">
       <c r="A13" t="s">
-        <v>66</v>
+        <v>64</v>
       </c>
     </row>
   </sheetData>

--- a/tests/AddOn_Input_92111_v03.xlsx
+++ b/tests/AddOn_Input_92111_v03.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\marco\Documents\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{7E0025BC-9204-4D1F-A25A-53A7D90806D3}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{7FB1D4FE-5196-4E0B-BFFF-943FBE60897D}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-93" yWindow="-93" windowWidth="25786" windowHeight="13866" activeTab="3" xr2:uid="{FA0E1F60-FDE8-4B1B-B207-153282F6AB0E}"/>
   </bookViews>
@@ -2882,7 +2882,7 @@
         <v>104</v>
       </c>
       <c r="C10" t="s">
-        <v>134</v>
+        <v>156</v>
       </c>
     </row>
     <row r="11" spans="1:3">
@@ -2893,7 +2893,7 @@
         <v>104</v>
       </c>
       <c r="C11" t="s">
-        <v>134</v>
+        <v>156</v>
       </c>
     </row>
     <row r="12" spans="1:3">
@@ -2904,7 +2904,7 @@
         <v>104</v>
       </c>
       <c r="C12" t="s">
-        <v>134</v>
+        <v>156</v>
       </c>
     </row>
     <row r="13" spans="1:3">
@@ -2915,7 +2915,7 @@
         <v>104</v>
       </c>
       <c r="C13" t="s">
-        <v>134</v>
+        <v>156</v>
       </c>
     </row>
     <row r="14" spans="1:3">
@@ -2926,7 +2926,7 @@
         <v>104</v>
       </c>
       <c r="C14" t="s">
-        <v>134</v>
+        <v>156</v>
       </c>
     </row>
     <row r="15" spans="1:3">
@@ -2937,7 +2937,7 @@
         <v>104</v>
       </c>
       <c r="C15" t="s">
-        <v>134</v>
+        <v>156</v>
       </c>
     </row>
     <row r="16" spans="1:3">
@@ -2948,7 +2948,7 @@
         <v>104</v>
       </c>
       <c r="C16" t="s">
-        <v>134</v>
+        <v>156</v>
       </c>
     </row>
     <row r="17" spans="1:3">
@@ -2959,7 +2959,7 @@
         <v>104</v>
       </c>
       <c r="C17" t="s">
-        <v>134</v>
+        <v>156</v>
       </c>
     </row>
     <row r="18" spans="1:3">
@@ -2970,7 +2970,7 @@
         <v>104</v>
       </c>
       <c r="C18" t="s">
-        <v>134</v>
+        <v>156</v>
       </c>
     </row>
     <row r="19" spans="1:3">
@@ -2981,7 +2981,7 @@
         <v>104</v>
       </c>
       <c r="C19" t="s">
-        <v>134</v>
+        <v>156</v>
       </c>
     </row>
     <row r="20" spans="1:3">
@@ -2992,7 +2992,7 @@
         <v>104</v>
       </c>
       <c r="C20" t="s">
-        <v>134</v>
+        <v>156</v>
       </c>
     </row>
     <row r="21" spans="1:3">
@@ -3003,7 +3003,7 @@
         <v>104</v>
       </c>
       <c r="C21" t="s">
-        <v>134</v>
+        <v>156</v>
       </c>
     </row>
     <row r="22" spans="1:3">
@@ -3014,7 +3014,7 @@
         <v>104</v>
       </c>
       <c r="C22" t="s">
-        <v>134</v>
+        <v>156</v>
       </c>
     </row>
     <row r="23" spans="1:3">
@@ -3025,7 +3025,7 @@
         <v>104</v>
       </c>
       <c r="C23" t="s">
-        <v>134</v>
+        <v>156</v>
       </c>
     </row>
     <row r="24" spans="1:3">
@@ -3036,7 +3036,7 @@
         <v>104</v>
       </c>
       <c r="C24" t="s">
-        <v>134</v>
+        <v>156</v>
       </c>
     </row>
     <row r="25" spans="1:3">
@@ -3047,7 +3047,7 @@
         <v>104</v>
       </c>
       <c r="C25" t="s">
-        <v>134</v>
+        <v>156</v>
       </c>
     </row>
     <row r="26" spans="1:3">
@@ -3058,7 +3058,7 @@
         <v>104</v>
       </c>
       <c r="C26" t="s">
-        <v>134</v>
+        <v>156</v>
       </c>
     </row>
     <row r="27" spans="1:3">
@@ -3069,7 +3069,7 @@
         <v>104</v>
       </c>
       <c r="C27" t="s">
-        <v>134</v>
+        <v>156</v>
       </c>
     </row>
     <row r="28" spans="1:3">
@@ -3080,7 +3080,7 @@
         <v>104</v>
       </c>
       <c r="C28" t="s">
-        <v>134</v>
+        <v>156</v>
       </c>
     </row>
     <row r="29" spans="1:3">
@@ -3091,7 +3091,7 @@
         <v>104</v>
       </c>
       <c r="C29" t="s">
-        <v>134</v>
+        <v>156</v>
       </c>
     </row>
     <row r="30" spans="1:3">
@@ -3102,7 +3102,7 @@
         <v>104</v>
       </c>
       <c r="C30" t="s">
-        <v>134</v>
+        <v>156</v>
       </c>
     </row>
     <row r="31" spans="1:3">
@@ -3113,7 +3113,7 @@
         <v>104</v>
       </c>
       <c r="C31" t="s">
-        <v>134</v>
+        <v>156</v>
       </c>
     </row>
     <row r="32" spans="1:3">
@@ -3124,7 +3124,7 @@
         <v>104</v>
       </c>
       <c r="C32" t="s">
-        <v>134</v>
+        <v>156</v>
       </c>
     </row>
     <row r="33" spans="1:3">
@@ -3135,7 +3135,7 @@
         <v>104</v>
       </c>
       <c r="C33" t="s">
-        <v>134</v>
+        <v>156</v>
       </c>
     </row>
     <row r="34" spans="1:3">
@@ -3146,7 +3146,7 @@
         <v>104</v>
       </c>
       <c r="C34" t="s">
-        <v>134</v>
+        <v>156</v>
       </c>
     </row>
     <row r="35" spans="1:3">
@@ -3157,7 +3157,7 @@
         <v>104</v>
       </c>
       <c r="C35" t="s">
-        <v>134</v>
+        <v>156</v>
       </c>
     </row>
     <row r="36" spans="1:3">
@@ -3168,7 +3168,7 @@
         <v>104</v>
       </c>
       <c r="C36" t="s">
-        <v>134</v>
+        <v>156</v>
       </c>
     </row>
     <row r="37" spans="1:3">
@@ -3179,7 +3179,7 @@
         <v>104</v>
       </c>
       <c r="C37" t="s">
-        <v>134</v>
+        <v>156</v>
       </c>
     </row>
   </sheetData>
@@ -3190,7 +3190,7 @@
   <pageMargins left="0.7" right="0.7" top="0.78740157499999996" bottom="0.78740157499999996" header="0.3" footer="0.3"/>
   <extLst>
     <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{CCE6A557-97BC-4b89-ADB6-D9C93CAAB3DF}">
-      <x14:dataValidations xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main" count="3">
+      <x14:dataValidations xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main" count="4">
         <x14:dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" xr:uid="{64C27FEB-0949-4523-8ACE-6A67A7590785}">
           <x14:formula1>
             <xm:f>Hidden_Lists!$F$2:$F$30</xm:f>
@@ -3207,7 +3207,13 @@
           <x14:formula1>
             <xm:f>Basics!$F$10:$F$100</xm:f>
           </x14:formula1>
-          <xm:sqref>C10:C165</xm:sqref>
+          <xm:sqref>C38:C165</xm:sqref>
+        </x14:dataValidation>
+        <x14:dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" xr:uid="{2ABC38E8-74A5-4DDA-9343-529BA5664FEF}">
+          <x14:formula1>
+            <xm:f>Basics!$E$10:$E$100</xm:f>
+          </x14:formula1>
+          <xm:sqref>C10:C37</xm:sqref>
         </x14:dataValidation>
       </x14:dataValidations>
     </ext>
